--- a/research/traditional_assets/database/data/netherlands/netherlands_computer_services.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_computer_services.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08876607688964792</v>
+        <v>0.08860755041127265</v>
       </c>
       <c r="C2">
-        <v>51.83019208017351</v>
+        <v>51.37352975523249</v>
       </c>
       <c r="D2">
-        <v>49.30019208017351</v>
+        <v>49.37942975523249</v>
       </c>
       <c r="E2">
-        <v>-9.890000000000001</v>
+        <v>-9.354100000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.5359</v>
       </c>
       <c r="G2">
         <v>2.53</v>
@@ -1576,45 +1576,45 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02963527</v>
       </c>
       <c r="N2">
-        <v>0.1600000000000001</v>
+        <v>0.1303647300000002</v>
       </c>
       <c r="O2">
-        <v>0.04128000000000004</v>
+        <v>0.03363410034000004</v>
       </c>
       <c r="P2">
-        <v>0.1187200000000001</v>
+        <v>0.09673062966000011</v>
       </c>
       <c r="Q2">
-        <v>5.548719999999999</v>
+        <v>5.526730629659999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08876607688964792</v>
+        <v>0.08908810546593196</v>
       </c>
       <c r="T2">
-        <v>0.9922881498763956</v>
+        <v>0.999725299444156</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
+        <v>0.0553</v>
       </c>
       <c r="V2">
         <v>0.258</v>
       </c>
       <c r="W2">
-        <v>0.0373226</v>
+        <v>0.0410326</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>5.39897223814732</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08860755041127265</v>
+        <v>0.08896397193289736</v>
       </c>
       <c r="C3">
-        <v>51.37352975523249</v>
+        <v>50.65983262993647</v>
       </c>
       <c r="D3">
-        <v>49.37942975523249</v>
+        <v>49.20163262993648</v>
       </c>
       <c r="E3">
-        <v>-9.354100000000001</v>
+        <v>-8.818200000000001</v>
       </c>
       <c r="F3">
-        <v>0.5359</v>
+        <v>1.0718</v>
       </c>
       <c r="G3">
         <v>2.53</v>
@@ -1658,45 +1658,45 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M3">
-        <v>0.02963527</v>
+        <v>0.09646200000000001</v>
       </c>
       <c r="N3">
-        <v>0.1303647300000002</v>
+        <v>0.06353800000000014</v>
       </c>
       <c r="O3">
-        <v>0.03363410034000004</v>
+        <v>0.01639280400000004</v>
       </c>
       <c r="P3">
-        <v>0.09673062966000011</v>
+        <v>0.0471451960000001</v>
       </c>
       <c r="Q3">
-        <v>5.526730629659999</v>
+        <v>5.477145195999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08908810546593196</v>
+        <v>0.08941670605397689</v>
       </c>
       <c r="T3">
-        <v>0.999725299444156</v>
+        <v>1.007314227574524</v>
       </c>
       <c r="U3">
-        <v>0.0553</v>
+        <v>0.09</v>
       </c>
       <c r="V3">
         <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.0410326</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y3">
-        <v>5.39897223814732</v>
+        <v>1.658684248719704</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08896397193289736</v>
+        <v>0.09355542571094506</v>
       </c>
       <c r="C4">
-        <v>50.65983262993647</v>
+        <v>47.94294336305571</v>
       </c>
       <c r="D4">
-        <v>49.20163262993648</v>
+        <v>47.02064336305571</v>
       </c>
       <c r="E4">
-        <v>-8.818200000000001</v>
+        <v>-8.282300000000001</v>
       </c>
       <c r="F4">
-        <v>1.0718</v>
+        <v>1.6077</v>
       </c>
       <c r="G4">
         <v>2.53</v>
@@ -1740,45 +1740,45 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M4">
-        <v>0.09646200000000001</v>
+        <v>0.3790956600000001</v>
       </c>
       <c r="N4">
-        <v>0.06353800000000014</v>
+        <v>-0.2190956599999999</v>
       </c>
       <c r="O4">
-        <v>0.01639280400000004</v>
+        <v>-0.05652668027999998</v>
       </c>
       <c r="P4">
-        <v>0.0471451960000001</v>
+        <v>-0.16256897972</v>
       </c>
       <c r="Q4">
-        <v>5.477145195999999</v>
+        <v>5.26743102028</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08941670605397689</v>
+        <v>0.08995022543922732</v>
       </c>
       <c r="T4">
-        <v>1.007314227574524</v>
+        <v>1.01963569143712</v>
       </c>
       <c r="U4">
-        <v>0.09</v>
+        <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>0.258</v>
+        <v>0.1088907216716753</v>
       </c>
       <c r="W4">
-        <v>0.06677999999999999</v>
+        <v>0.210123567829819</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y4">
-        <v>1.658684248719704</v>
+        <v>0.4220570607429273</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09355542571094506</v>
+        <v>0.09545542571094506</v>
       </c>
       <c r="C5">
-        <v>47.94294336305571</v>
+        <v>46.56006609080227</v>
       </c>
       <c r="D5">
-        <v>47.02064336305571</v>
+        <v>46.17366609080227</v>
       </c>
       <c r="E5">
-        <v>-8.282300000000001</v>
+        <v>-7.7464</v>
       </c>
       <c r="F5">
-        <v>1.6077</v>
+        <v>2.1436</v>
       </c>
       <c r="G5">
         <v>2.53</v>
@@ -1822,37 +1822,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M5">
-        <v>0.3790956600000001</v>
+        <v>0.5054608800000001</v>
       </c>
       <c r="N5">
-        <v>-0.2190956599999999</v>
+        <v>-0.34546088</v>
       </c>
       <c r="O5">
-        <v>-0.05652668027999998</v>
+        <v>-0.08912890704</v>
       </c>
       <c r="P5">
-        <v>-0.16256897972</v>
+        <v>-0.25633197296</v>
       </c>
       <c r="Q5">
-        <v>5.26743102028</v>
+        <v>5.17366802704</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08995022543922732</v>
+        <v>0.09041012362088593</v>
       </c>
       <c r="T5">
-        <v>1.01963569143712</v>
+        <v>1.030256896556257</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>0.1088907216716753</v>
+        <v>0.08166804125375643</v>
       </c>
       <c r="W5">
-        <v>0.210123567829819</v>
+        <v>0.2165426758723642</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>0.4220570607429273</v>
+        <v>0.3165427955571954</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09545542571094506</v>
+        <v>0.09735542571094505</v>
       </c>
       <c r="C6">
-        <v>46.56006609080227</v>
+        <v>45.20716191895336</v>
       </c>
       <c r="D6">
-        <v>46.17366609080227</v>
+        <v>45.35666191895336</v>
       </c>
       <c r="E6">
-        <v>-7.7464</v>
+        <v>-7.2105</v>
       </c>
       <c r="F6">
-        <v>2.1436</v>
+        <v>2.6795</v>
       </c>
       <c r="G6">
         <v>2.53</v>
@@ -1904,37 +1904,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M6">
-        <v>0.5054608800000001</v>
+        <v>0.6318261000000002</v>
       </c>
       <c r="N6">
-        <v>-0.34546088</v>
+        <v>-0.4718261</v>
       </c>
       <c r="O6">
-        <v>-0.08912890704</v>
+        <v>-0.1217311338</v>
       </c>
       <c r="P6">
-        <v>-0.25633197296</v>
+        <v>-0.3500949662</v>
       </c>
       <c r="Q6">
-        <v>5.17366802704</v>
+        <v>5.079905033799999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09041012362088593</v>
+        <v>0.09087970386952683</v>
       </c>
       <c r="T6">
-        <v>1.030256896556257</v>
+        <v>1.041101705993691</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>0.08166804125375643</v>
+        <v>0.06533443300300515</v>
       </c>
       <c r="W6">
-        <v>0.2165426758723642</v>
+        <v>0.2203941406978914</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>0.3165427955571954</v>
+        <v>0.2532342364457564</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09735542571094505</v>
+        <v>0.09925542571094506</v>
       </c>
       <c r="C7">
-        <v>45.20716191895336</v>
+        <v>43.88266746388811</v>
       </c>
       <c r="D7">
-        <v>45.35666191895336</v>
+        <v>44.56806746388811</v>
       </c>
       <c r="E7">
-        <v>-7.2105</v>
+        <v>-6.6746</v>
       </c>
       <c r="F7">
-        <v>2.6795</v>
+        <v>3.2154</v>
       </c>
       <c r="G7">
         <v>2.53</v>
@@ -1986,37 +1986,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M7">
-        <v>0.6318261000000002</v>
+        <v>0.7581913200000001</v>
       </c>
       <c r="N7">
-        <v>-0.4718261</v>
+        <v>-0.59819132</v>
       </c>
       <c r="O7">
-        <v>-0.1217311338</v>
+        <v>-0.15433336056</v>
       </c>
       <c r="P7">
-        <v>-0.3500949662</v>
+        <v>-0.4438579594399999</v>
       </c>
       <c r="Q7">
-        <v>5.079905033799999</v>
+        <v>4.98614204056</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09087970386952683</v>
+        <v>0.09135927518728776</v>
       </c>
       <c r="T7">
-        <v>1.041101705993691</v>
+        <v>1.052177256057454</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>0.06533443300300515</v>
+        <v>0.05444536083583763</v>
       </c>
       <c r="W7">
-        <v>0.2203941406978914</v>
+        <v>0.2229617839149095</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>0.2532342364457564</v>
+        <v>0.2110285303714636</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09925542571094506</v>
+        <v>0.1011554257109451</v>
       </c>
       <c r="C8">
-        <v>43.88266746388811</v>
+        <v>42.5851262110987</v>
       </c>
       <c r="D8">
-        <v>44.56806746388811</v>
+        <v>43.8064262110987</v>
       </c>
       <c r="E8">
-        <v>-6.6746</v>
+        <v>-6.138700000000001</v>
       </c>
       <c r="F8">
-        <v>3.2154</v>
+        <v>3.7513</v>
       </c>
       <c r="G8">
         <v>2.53</v>
@@ -2068,37 +2068,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M8">
-        <v>0.7581913200000001</v>
+        <v>0.8845565399999999</v>
       </c>
       <c r="N8">
-        <v>-0.59819132</v>
+        <v>-0.7245565399999998</v>
       </c>
       <c r="O8">
-        <v>-0.15433336056</v>
+        <v>-0.18693558732</v>
       </c>
       <c r="P8">
-        <v>-0.4438579594399999</v>
+        <v>-0.5376209526799999</v>
       </c>
       <c r="Q8">
-        <v>4.98614204056</v>
+        <v>4.89237904732</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09135927518728776</v>
+        <v>0.09184915986672096</v>
       </c>
       <c r="T8">
-        <v>1.052177256057454</v>
+        <v>1.063490989993556</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>0.05444536083583763</v>
+        <v>0.04666745214500369</v>
       </c>
       <c r="W8">
-        <v>0.2229617839149095</v>
+        <v>0.2247958147842082</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>0.2110285303714636</v>
+        <v>0.1808815974612547</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1011554257109451</v>
+        <v>0.1030554257109451</v>
       </c>
       <c r="C9">
-        <v>42.58512621109871</v>
+        <v>41.31317953698073</v>
       </c>
       <c r="D9">
-        <v>43.80642621109871</v>
+        <v>43.07037953698072</v>
       </c>
       <c r="E9">
-        <v>-6.1387</v>
+        <v>-5.6028</v>
       </c>
       <c r="F9">
-        <v>3.751300000000001</v>
+        <v>4.2872</v>
       </c>
       <c r="G9">
         <v>2.53</v>
@@ -2150,37 +2150,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M9">
-        <v>0.8845565400000002</v>
+        <v>1.01092176</v>
       </c>
       <c r="N9">
-        <v>-0.72455654</v>
+        <v>-0.8509217600000001</v>
       </c>
       <c r="O9">
-        <v>-0.18693558732</v>
+        <v>-0.21953781408</v>
       </c>
       <c r="P9">
-        <v>-0.53762095268</v>
+        <v>-0.63138394592</v>
       </c>
       <c r="Q9">
-        <v>4.89237904732</v>
+        <v>4.79861605408</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09184915986672096</v>
+        <v>0.09234969421309835</v>
       </c>
       <c r="T9">
-        <v>1.063490989993556</v>
+        <v>1.075050674667399</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>0.04666745214500367</v>
+        <v>0.04083402062687821</v>
       </c>
       <c r="W9">
-        <v>0.2247958147842082</v>
+        <v>0.2261713379361821</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>0.1808815974612545</v>
+        <v>0.1582713977785978</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1030554257109451</v>
+        <v>0.1049554257109451</v>
       </c>
       <c r="C10">
-        <v>41.31317953698073</v>
+        <v>40.06555862079162</v>
       </c>
       <c r="D10">
-        <v>43.07037953698072</v>
+        <v>42.35865862079162</v>
       </c>
       <c r="E10">
-        <v>-5.6028</v>
+        <v>-5.0669</v>
       </c>
       <c r="F10">
-        <v>4.2872</v>
+        <v>4.8231</v>
       </c>
       <c r="G10">
         <v>2.53</v>
@@ -2232,37 +2232,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M10">
-        <v>1.01092176</v>
+        <v>1.13728698</v>
       </c>
       <c r="N10">
-        <v>-0.8509217600000001</v>
+        <v>-0.9772869799999999</v>
       </c>
       <c r="O10">
-        <v>-0.21953781408</v>
+        <v>-0.25214004084</v>
       </c>
       <c r="P10">
-        <v>-0.63138394592</v>
+        <v>-0.7251469391599999</v>
       </c>
       <c r="Q10">
-        <v>4.79861605408</v>
+        <v>4.70485306084</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09234969421309835</v>
+        <v>0.09286122931434121</v>
       </c>
       <c r="T10">
-        <v>1.075050674667399</v>
+        <v>1.086864418345062</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>0.04083402062687821</v>
+        <v>0.03629690722389175</v>
       </c>
       <c r="W10">
-        <v>0.2261713379361821</v>
+        <v>0.2272411892766063</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.1582713977785978</v>
+        <v>0.1406856869143092</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1049554257109451</v>
+        <v>0.1068554257109451</v>
       </c>
       <c r="C11">
-        <v>40.06555862079162</v>
+        <v>38.84107714548353</v>
       </c>
       <c r="D11">
-        <v>42.35865862079162</v>
+        <v>41.67007714548353</v>
       </c>
       <c r="E11">
-        <v>-5.0669</v>
+        <v>-4.531000000000001</v>
       </c>
       <c r="F11">
-        <v>4.8231</v>
+        <v>5.359</v>
       </c>
       <c r="G11">
         <v>2.53</v>
@@ -2314,37 +2314,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M11">
-        <v>1.13728698</v>
+        <v>1.2636522</v>
       </c>
       <c r="N11">
-        <v>-0.9772869799999999</v>
+        <v>-1.1036522</v>
       </c>
       <c r="O11">
-        <v>-0.25214004084</v>
+        <v>-0.2847422676</v>
       </c>
       <c r="P11">
-        <v>-0.7251469391599999</v>
+        <v>-0.8189099324</v>
       </c>
       <c r="Q11">
-        <v>4.70485306084</v>
+        <v>4.611090067599999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09286122931434121</v>
+        <v>0.09338413186227833</v>
       </c>
       <c r="T11">
-        <v>1.086864418345062</v>
+        <v>1.098940689660008</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.03629690722389175</v>
+        <v>0.03266721650150257</v>
       </c>
       <c r="W11">
-        <v>0.2272411892766063</v>
+        <v>0.2280970703489457</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.1406856869143092</v>
+        <v>0.1266171182228782</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1068554257109451</v>
+        <v>0.1087554257109451</v>
       </c>
       <c r="C12">
-        <v>38.84107714548353</v>
+        <v>37.63862469907853</v>
       </c>
       <c r="D12">
-        <v>41.67007714548353</v>
+        <v>41.00352469907853</v>
       </c>
       <c r="E12">
-        <v>-4.531</v>
+        <v>-3.9951</v>
       </c>
       <c r="F12">
-        <v>5.359000000000001</v>
+        <v>5.894900000000001</v>
       </c>
       <c r="G12">
         <v>2.53</v>
@@ -2396,37 +2396,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M12">
-        <v>1.2636522</v>
+        <v>1.39001742</v>
       </c>
       <c r="N12">
-        <v>-1.1036522</v>
+        <v>-1.23001742</v>
       </c>
       <c r="O12">
-        <v>-0.2847422676</v>
+        <v>-0.31734449436</v>
       </c>
       <c r="P12">
-        <v>-0.8189099324000002</v>
+        <v>-0.91267292564</v>
       </c>
       <c r="Q12">
-        <v>4.611090067599999</v>
+        <v>4.51732707436</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09338413186227833</v>
+        <v>0.09391878502927022</v>
       </c>
       <c r="T12">
-        <v>1.098940689660008</v>
+        <v>1.111288337858435</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.03266721650150257</v>
+        <v>0.02969746954682052</v>
       </c>
       <c r="W12">
-        <v>0.2280970703489457</v>
+        <v>0.2287973366808597</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.1266171182228781</v>
+        <v>0.1151064711117075</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1087554257109451</v>
+        <v>0.1106554257109451</v>
       </c>
       <c r="C13">
-        <v>37.63862469907853</v>
+        <v>36.45716079938077</v>
       </c>
       <c r="D13">
-        <v>41.00352469907853</v>
+        <v>40.35796079938076</v>
       </c>
       <c r="E13">
-        <v>-3.9951</v>
+        <v>-3.4592</v>
       </c>
       <c r="F13">
-        <v>5.894900000000001</v>
+        <v>6.430800000000001</v>
       </c>
       <c r="G13">
         <v>2.53</v>
@@ -2478,37 +2478,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M13">
-        <v>1.39001742</v>
+        <v>1.51638264</v>
       </c>
       <c r="N13">
-        <v>-1.23001742</v>
+        <v>-1.35638264</v>
       </c>
       <c r="O13">
-        <v>-0.31734449436</v>
+        <v>-0.34994672112</v>
       </c>
       <c r="P13">
-        <v>-0.91267292564</v>
+        <v>-1.00643591888</v>
       </c>
       <c r="Q13">
-        <v>4.51732707436</v>
+        <v>4.423564081119999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09391878502927022</v>
+        <v>0.09446558940460284</v>
       </c>
       <c r="T13">
-        <v>1.111288337858435</v>
+        <v>1.123916614425008</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.02969746954682052</v>
+        <v>0.02722268041791881</v>
       </c>
       <c r="W13">
-        <v>0.2287973366808597</v>
+        <v>0.2293808919574547</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.1151064711117075</v>
+        <v>0.1055142651857318</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1106554257109451</v>
+        <v>0.1125554257109451</v>
       </c>
       <c r="C14">
-        <v>36.45716079938077</v>
+        <v>35.29570947439299</v>
       </c>
       <c r="D14">
-        <v>40.35796079938076</v>
+        <v>39.73240947439299</v>
       </c>
       <c r="E14">
-        <v>-3.4592</v>
+        <v>-2.9233</v>
       </c>
       <c r="F14">
-        <v>6.430800000000001</v>
+        <v>6.9667</v>
       </c>
       <c r="G14">
         <v>2.53</v>
@@ -2560,37 +2560,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M14">
-        <v>1.51638264</v>
+        <v>1.64274786</v>
       </c>
       <c r="N14">
-        <v>-1.35638264</v>
+        <v>-1.48274786</v>
       </c>
       <c r="O14">
-        <v>-0.34994672112</v>
+        <v>-0.38254894788</v>
       </c>
       <c r="P14">
-        <v>-1.00643591888</v>
+        <v>-1.10019891212</v>
       </c>
       <c r="Q14">
-        <v>4.423564081119999</v>
+        <v>4.32980108788</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09446558940460284</v>
+        <v>0.09502496399546034</v>
       </c>
       <c r="T14">
-        <v>1.123916614425008</v>
+        <v>1.136835196200008</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.02722268041791881</v>
+        <v>0.02512862807807891</v>
       </c>
       <c r="W14">
-        <v>0.2293808919574547</v>
+        <v>0.229874669499189</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.1055142651857318</v>
+        <v>0.0973977832483679</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1125554257109451</v>
+        <v>0.1144554257109451</v>
       </c>
       <c r="C15">
-        <v>35.29570947439299</v>
+        <v>34.15335433906348</v>
       </c>
       <c r="D15">
-        <v>39.73240947439299</v>
+        <v>39.12595433906348</v>
       </c>
       <c r="E15">
-        <v>-2.9233</v>
+        <v>-2.3874</v>
       </c>
       <c r="F15">
-        <v>6.9667</v>
+        <v>7.502600000000001</v>
       </c>
       <c r="G15">
         <v>2.53</v>
@@ -2642,37 +2642,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M15">
-        <v>1.64274786</v>
+        <v>1.76911308</v>
       </c>
       <c r="N15">
-        <v>-1.48274786</v>
+        <v>-1.60911308</v>
       </c>
       <c r="O15">
-        <v>-0.38254894788</v>
+        <v>-0.4151511746400001</v>
       </c>
       <c r="P15">
-        <v>-1.10019891212</v>
+        <v>-1.19396190536</v>
       </c>
       <c r="Q15">
-        <v>4.32980108788</v>
+        <v>4.23603809464</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09502496399546034</v>
+        <v>0.09559734729773312</v>
       </c>
       <c r="T15">
-        <v>1.136835196200008</v>
+        <v>1.15005421010931</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.02512862807807891</v>
+        <v>0.02333372607250184</v>
       </c>
       <c r="W15">
-        <v>0.229874669499189</v>
+        <v>0.2302979073921041</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.0973977832483679</v>
+        <v>0.09044079873062727</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1144554257109451</v>
+        <v>0.1163554257109451</v>
       </c>
       <c r="C16">
-        <v>34.15335433906348</v>
+        <v>33.0292341161305</v>
       </c>
       <c r="D16">
-        <v>39.12595433906348</v>
+        <v>38.5377341161305</v>
       </c>
       <c r="E16">
-        <v>-2.3874</v>
+        <v>-1.8515</v>
       </c>
       <c r="F16">
-        <v>7.502600000000001</v>
+        <v>8.038500000000001</v>
       </c>
       <c r="G16">
         <v>2.53</v>
@@ -2724,37 +2724,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M16">
-        <v>1.76911308</v>
+        <v>1.8954783</v>
       </c>
       <c r="N16">
-        <v>-1.60911308</v>
+        <v>-1.7354783</v>
       </c>
       <c r="O16">
-        <v>-0.4151511746400001</v>
+        <v>-0.4477534014</v>
       </c>
       <c r="P16">
-        <v>-1.19396190536</v>
+        <v>-1.2877248986</v>
       </c>
       <c r="Q16">
-        <v>4.23603809464</v>
+        <v>4.142275101399999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09559734729773312</v>
+        <v>0.09618319844241235</v>
       </c>
       <c r="T16">
-        <v>1.15005421010931</v>
+        <v>1.163584259640008</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.02333372607250184</v>
+        <v>0.02177814433433505</v>
       </c>
       <c r="W16">
-        <v>0.2302979073921041</v>
+        <v>0.2306647135659638</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.09044079873062727</v>
+        <v>0.0844114121485855</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1163554257109451</v>
+        <v>0.1182554257109451</v>
       </c>
       <c r="C17">
-        <v>33.02923411613051</v>
+        <v>31.92253855502085</v>
       </c>
       <c r="D17">
-        <v>38.53773411613051</v>
+        <v>37.96693855502085</v>
       </c>
       <c r="E17">
-        <v>-1.8515</v>
+        <v>-1.3156</v>
       </c>
       <c r="F17">
-        <v>8.038500000000001</v>
+        <v>8.574400000000001</v>
       </c>
       <c r="G17">
         <v>2.53</v>
@@ -2806,37 +2806,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M17">
-        <v>1.8954783</v>
+        <v>2.02184352</v>
       </c>
       <c r="N17">
-        <v>-1.7354783</v>
+        <v>-1.86184352</v>
       </c>
       <c r="O17">
-        <v>-0.4477534014</v>
+        <v>-0.4803556281600001</v>
       </c>
       <c r="P17">
-        <v>-1.2877248986</v>
+        <v>-1.38148789184</v>
       </c>
       <c r="Q17">
-        <v>4.142275101399999</v>
+        <v>4.04851210816</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09618319844241235</v>
+        <v>0.09678299842386963</v>
       </c>
       <c r="T17">
-        <v>1.163584259640008</v>
+        <v>1.177436453207151</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.02177814433433505</v>
+        <v>0.02041701031343911</v>
       </c>
       <c r="W17">
-        <v>0.2306647135659638</v>
+        <v>0.2309856689680911</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.0844114121485855</v>
+        <v>0.07913569888929883</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1182554257109451</v>
+        <v>0.1201554257109451</v>
       </c>
       <c r="C18">
-        <v>31.92253855502085</v>
+        <v>30.83250470813423</v>
       </c>
       <c r="D18">
-        <v>37.96693855502085</v>
+        <v>37.41280470813423</v>
       </c>
       <c r="E18">
-        <v>-1.3156</v>
+        <v>-0.7797000000000001</v>
       </c>
       <c r="F18">
-        <v>8.574400000000001</v>
+        <v>9.110300000000001</v>
       </c>
       <c r="G18">
         <v>2.53</v>
@@ -2888,37 +2888,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M18">
-        <v>2.02184352</v>
+        <v>2.14820874</v>
       </c>
       <c r="N18">
-        <v>-1.86184352</v>
+        <v>-1.98820874</v>
       </c>
       <c r="O18">
-        <v>-0.4803556281600001</v>
+        <v>-0.51295785492</v>
       </c>
       <c r="P18">
-        <v>-1.38148789184</v>
+        <v>-1.47525088508</v>
       </c>
       <c r="Q18">
-        <v>4.04851210816</v>
+        <v>3.954749114919999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09678299842386963</v>
+        <v>0.09739725141692832</v>
       </c>
       <c r="T18">
-        <v>1.177436453207151</v>
+        <v>1.191622434571093</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.02041701031343911</v>
+        <v>0.01921600970676622</v>
       </c>
       <c r="W18">
-        <v>0.2309856689680911</v>
+        <v>0.2312688649111445</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.07913569888929883</v>
+        <v>0.07448065777816359</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1201554257109451</v>
+        <v>0.1220554257109451</v>
       </c>
       <c r="C19">
-        <v>30.83250470813423</v>
+        <v>29.75841352852652</v>
       </c>
       <c r="D19">
-        <v>37.41280470813423</v>
+        <v>36.87461352852652</v>
       </c>
       <c r="E19">
-        <v>-0.7797000000000001</v>
+        <v>-0.2437999999999985</v>
       </c>
       <c r="F19">
-        <v>9.110300000000001</v>
+        <v>9.646200000000002</v>
       </c>
       <c r="G19">
         <v>2.53</v>
@@ -2970,37 +2970,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M19">
-        <v>2.14820874</v>
+        <v>2.274573960000001</v>
       </c>
       <c r="N19">
-        <v>-1.98820874</v>
+        <v>-2.11457396</v>
       </c>
       <c r="O19">
-        <v>-0.51295785492</v>
+        <v>-0.5455600816800001</v>
       </c>
       <c r="P19">
-        <v>-1.47525088508</v>
+        <v>-1.56901387832</v>
       </c>
       <c r="Q19">
-        <v>3.954749114919999</v>
+        <v>3.860986121679999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09739725141692832</v>
+        <v>0.09802648619030549</v>
       </c>
       <c r="T19">
-        <v>1.191622434571093</v>
+        <v>1.206154415480496</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.01921600970676622</v>
+        <v>0.01814845361194587</v>
       </c>
       <c r="W19">
-        <v>0.2312688649111445</v>
+        <v>0.2315205946383032</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.07448065777816359</v>
+        <v>0.07034284345715458</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1220554257109451</v>
+        <v>0.1239554257109451</v>
       </c>
       <c r="C20">
-        <v>29.75841352852652</v>
+        <v>28.69958675708688</v>
       </c>
       <c r="D20">
-        <v>36.87461352852652</v>
+        <v>36.35168675708687</v>
       </c>
       <c r="E20">
-        <v>-0.2438000000000002</v>
+        <v>0.2920999999999996</v>
       </c>
       <c r="F20">
-        <v>9.6462</v>
+        <v>10.1821</v>
       </c>
       <c r="G20">
         <v>2.53</v>
@@ -3052,37 +3052,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M20">
-        <v>2.27457396</v>
+        <v>2.40093918</v>
       </c>
       <c r="N20">
-        <v>-2.11457396</v>
+        <v>-2.24093918</v>
       </c>
       <c r="O20">
-        <v>-0.54556008168</v>
+        <v>-0.5781623084399999</v>
       </c>
       <c r="P20">
-        <v>-1.56901387832</v>
+        <v>-1.66277687156</v>
       </c>
       <c r="Q20">
-        <v>3.86098612168</v>
+        <v>3.76722312844</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09802648619030548</v>
+        <v>0.09867125762475371</v>
       </c>
       <c r="T20">
-        <v>1.206154415480496</v>
+        <v>1.221045210733342</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.01814845361194587</v>
+        <v>0.0171932718428961</v>
       </c>
       <c r="W20">
-        <v>0.2315205946383032</v>
+        <v>0.2317458264994451</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.07034284345715458</v>
+        <v>0.06664058853835697</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1239554257109451</v>
+        <v>0.1258554257109451</v>
       </c>
       <c r="C21">
-        <v>28.69958675708688</v>
+        <v>27.65538407087288</v>
       </c>
       <c r="D21">
-        <v>36.35168675708687</v>
+        <v>35.84338407087288</v>
       </c>
       <c r="E21">
-        <v>0.2920999999999996</v>
+        <v>0.8280000000000012</v>
       </c>
       <c r="F21">
-        <v>10.1821</v>
+        <v>10.718</v>
       </c>
       <c r="G21">
         <v>2.53</v>
@@ -3134,37 +3134,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M21">
-        <v>2.40093918</v>
+        <v>2.527304400000001</v>
       </c>
       <c r="N21">
-        <v>-2.24093918</v>
+        <v>-2.367304400000001</v>
       </c>
       <c r="O21">
-        <v>-0.5781623084399999</v>
+        <v>-0.6107645352000002</v>
       </c>
       <c r="P21">
-        <v>-1.66277687156</v>
+        <v>-1.7565398648</v>
       </c>
       <c r="Q21">
-        <v>3.76722312844</v>
+        <v>3.673460135199999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09867125762475371</v>
+        <v>0.09933214834506313</v>
       </c>
       <c r="T21">
-        <v>1.221045210733342</v>
+        <v>1.236308275867509</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.0171932718428961</v>
+        <v>0.01633360825075129</v>
       </c>
       <c r="W21">
-        <v>0.2317458264994451</v>
+        <v>0.2319485351744729</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.06664058853835697</v>
+        <v>0.06330855911143907</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1258554257109451</v>
+        <v>0.1277554257109451</v>
       </c>
       <c r="C22">
-        <v>27.65538407087288</v>
+        <v>26.62520046739412</v>
       </c>
       <c r="D22">
-        <v>35.84338407087288</v>
+        <v>35.34910046739412</v>
       </c>
       <c r="E22">
-        <v>0.8280000000000012</v>
+        <v>1.363900000000001</v>
       </c>
       <c r="F22">
-        <v>10.718</v>
+        <v>11.2539</v>
       </c>
       <c r="G22">
         <v>2.53</v>
@@ -3216,37 +3216,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M22">
-        <v>2.527304400000001</v>
+        <v>2.653669620000001</v>
       </c>
       <c r="N22">
-        <v>-2.367304400000001</v>
+        <v>-2.49366962</v>
       </c>
       <c r="O22">
-        <v>-0.6107645352000002</v>
+        <v>-0.6433667619600001</v>
       </c>
       <c r="P22">
-        <v>-1.7565398648</v>
+        <v>-1.85030285804</v>
       </c>
       <c r="Q22">
-        <v>3.673460135199999</v>
+        <v>3.57969714196</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09933214834506313</v>
+        <v>0.1000097704760133</v>
       </c>
       <c r="T22">
-        <v>1.236308275867509</v>
+        <v>1.251957747713933</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.01633360825075129</v>
+        <v>0.01555581738166789</v>
       </c>
       <c r="W22">
-        <v>0.2319485351744729</v>
+        <v>0.2321319382614027</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.06330855911143907</v>
+        <v>0.06029386582041818</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1277554257109451</v>
+        <v>0.1296554257109451</v>
       </c>
       <c r="C23">
-        <v>26.62520046739412</v>
+        <v>25.60846386237751</v>
       </c>
       <c r="D23">
-        <v>35.34910046739412</v>
+        <v>34.86826386237751</v>
       </c>
       <c r="E23">
-        <v>1.363899999999999</v>
+        <v>1.899800000000001</v>
       </c>
       <c r="F23">
-        <v>11.2539</v>
+        <v>11.7898</v>
       </c>
       <c r="G23">
         <v>2.53</v>
@@ -3298,37 +3298,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M23">
-        <v>2.65366962</v>
+        <v>2.78003484</v>
       </c>
       <c r="N23">
-        <v>-2.49366962</v>
+        <v>-2.62003484</v>
       </c>
       <c r="O23">
-        <v>-0.64336676196</v>
+        <v>-0.6759689887200001</v>
       </c>
       <c r="P23">
-        <v>-1.85030285804</v>
+        <v>-1.94406585128</v>
       </c>
       <c r="Q23">
-        <v>3.57969714196</v>
+        <v>3.48593414872</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1000097704760133</v>
+        <v>0.1007047675333981</v>
       </c>
       <c r="T23">
-        <v>1.251957747713933</v>
+        <v>1.268008488069239</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.01555581738166789</v>
+        <v>0.01484873477341026</v>
       </c>
       <c r="W23">
-        <v>0.2321319382614027</v>
+        <v>0.2322986683404299</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.06029386582041818</v>
+        <v>0.05755323555585368</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1296554257109451</v>
+        <v>0.1315554257109451</v>
       </c>
       <c r="C24">
-        <v>25.60846386237751</v>
+        <v>24.60463288096035</v>
       </c>
       <c r="D24">
-        <v>34.86826386237751</v>
+        <v>34.40033288096035</v>
       </c>
       <c r="E24">
-        <v>1.899800000000001</v>
+        <v>2.435700000000001</v>
       </c>
       <c r="F24">
-        <v>11.7898</v>
+        <v>12.3257</v>
       </c>
       <c r="G24">
         <v>2.53</v>
@@ -3380,37 +3380,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M24">
-        <v>2.78003484</v>
+        <v>2.906400060000001</v>
       </c>
       <c r="N24">
-        <v>-2.62003484</v>
+        <v>-2.74640006</v>
       </c>
       <c r="O24">
-        <v>-0.6759689887200001</v>
+        <v>-0.7085712154800001</v>
       </c>
       <c r="P24">
-        <v>-1.94406585128</v>
+        <v>-2.03782884452</v>
       </c>
       <c r="Q24">
-        <v>3.48593414872</v>
+        <v>3.392171155479999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1007047675333981</v>
+        <v>0.1014178164624032</v>
       </c>
       <c r="T24">
-        <v>1.268008488069239</v>
+        <v>1.284476130771437</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.01484873477341026</v>
+        <v>0.01420313760934894</v>
       </c>
       <c r="W24">
-        <v>0.2322986683404299</v>
+        <v>0.2324509001517155</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.05755323555585368</v>
+        <v>0.0550509209664688</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1315554257109451</v>
+        <v>0.1334554257109451</v>
       </c>
       <c r="C25">
-        <v>24.60463288096035</v>
+        <v>23.61319482438061</v>
       </c>
       <c r="D25">
-        <v>34.40033288096035</v>
+        <v>33.94479482438061</v>
       </c>
       <c r="E25">
-        <v>2.435700000000001</v>
+        <v>2.9716</v>
       </c>
       <c r="F25">
-        <v>12.3257</v>
+        <v>12.8616</v>
       </c>
       <c r="G25">
         <v>2.53</v>
@@ -3462,37 +3462,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M25">
-        <v>2.906400060000001</v>
+        <v>3.03276528</v>
       </c>
       <c r="N25">
-        <v>-2.74640006</v>
+        <v>-2.87276528</v>
       </c>
       <c r="O25">
-        <v>-0.7085712154800001</v>
+        <v>-0.7411734422400001</v>
       </c>
       <c r="P25">
-        <v>-2.03782884452</v>
+        <v>-2.13159183776</v>
       </c>
       <c r="Q25">
-        <v>3.392171155479999</v>
+        <v>3.298408162239999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1014178164624032</v>
+        <v>0.1021496298369085</v>
       </c>
       <c r="T25">
-        <v>1.284476130771437</v>
+        <v>1.301377132492114</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.01420313760934894</v>
+        <v>0.01361134020895941</v>
       </c>
       <c r="W25">
-        <v>0.2324509001517155</v>
+        <v>0.2325904459787274</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.0550509209664688</v>
+        <v>0.05275713259286596</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.133455425710945</v>
+        <v>0.1353554257109451</v>
       </c>
       <c r="C26">
-        <v>23.61319482438061</v>
+        <v>22.63366379610977</v>
       </c>
       <c r="D26">
-        <v>33.94479482438062</v>
+        <v>33.50116379610977</v>
       </c>
       <c r="E26">
-        <v>2.9716</v>
+        <v>3.5075</v>
       </c>
       <c r="F26">
-        <v>12.8616</v>
+        <v>13.3975</v>
       </c>
       <c r="G26">
         <v>2.53</v>
@@ -3544,37 +3544,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M26">
-        <v>3.03276528</v>
+        <v>3.1591305</v>
       </c>
       <c r="N26">
-        <v>-2.87276528</v>
+        <v>-2.9991305</v>
       </c>
       <c r="O26">
-        <v>-0.7411734422400001</v>
+        <v>-0.7737756690000001</v>
       </c>
       <c r="P26">
-        <v>-2.13159183776</v>
+        <v>-2.225354831</v>
       </c>
       <c r="Q26">
-        <v>3.298408162239999</v>
+        <v>3.204645169</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1021496298369085</v>
+        <v>0.102900958234734</v>
       </c>
       <c r="T26">
-        <v>1.301377132492114</v>
+        <v>1.318728827592009</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.01361134020895941</v>
+        <v>0.01306688660060103</v>
       </c>
       <c r="W26">
-        <v>0.2325904459787274</v>
+        <v>0.2327188281395783</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.05275713259286596</v>
+        <v>0.05064684728915125</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1353554257109451</v>
+        <v>0.1372554257109451</v>
       </c>
       <c r="C27">
-        <v>22.63366379610977</v>
+        <v>21.66557897302949</v>
       </c>
       <c r="D27">
-        <v>33.50116379610977</v>
+        <v>33.06897897302949</v>
       </c>
       <c r="E27">
-        <v>3.5075</v>
+        <v>4.0434</v>
       </c>
       <c r="F27">
-        <v>13.3975</v>
+        <v>13.9334</v>
       </c>
       <c r="G27">
         <v>2.53</v>
@@ -3626,37 +3626,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M27">
-        <v>3.1591305</v>
+        <v>3.28549572</v>
       </c>
       <c r="N27">
-        <v>-2.9991305</v>
+        <v>-3.12549572</v>
       </c>
       <c r="O27">
-        <v>-0.7737756690000001</v>
+        <v>-0.80637789576</v>
       </c>
       <c r="P27">
-        <v>-2.225354831</v>
+        <v>-2.31911782424</v>
       </c>
       <c r="Q27">
-        <v>3.204645169</v>
+        <v>3.11088217576</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.102900958234734</v>
+        <v>0.1036725928054736</v>
       </c>
       <c r="T27">
-        <v>1.318728827592009</v>
+        <v>1.336549487424334</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.01306688660060103</v>
+        <v>0.01256431403903945</v>
       </c>
       <c r="W27">
-        <v>0.2327188281395783</v>
+        <v>0.2328373347495945</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.05064684728915125</v>
+        <v>0.04869889162418395</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1372554257109451</v>
+        <v>0.1391554257109451</v>
       </c>
       <c r="C28">
-        <v>21.66557897302949</v>
+        <v>20.70850300872096</v>
       </c>
       <c r="D28">
-        <v>33.06897897302949</v>
+        <v>32.64780300872096</v>
       </c>
       <c r="E28">
-        <v>4.0434</v>
+        <v>4.579300000000002</v>
       </c>
       <c r="F28">
-        <v>13.9334</v>
+        <v>14.4693</v>
       </c>
       <c r="G28">
         <v>2.53</v>
@@ -3708,37 +3708,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M28">
-        <v>3.28549572</v>
+        <v>3.411860940000001</v>
       </c>
       <c r="N28">
-        <v>-3.12549572</v>
+        <v>-3.251860940000001</v>
       </c>
       <c r="O28">
-        <v>-0.80637789576</v>
+        <v>-0.8389801225200002</v>
       </c>
       <c r="P28">
-        <v>-2.31911782424</v>
+        <v>-2.41288081748</v>
       </c>
       <c r="Q28">
-        <v>3.11088217576</v>
+        <v>3.017119182519999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1036725928054736</v>
+        <v>0.1044653680493842</v>
       </c>
       <c r="T28">
-        <v>1.336549487424334</v>
+        <v>1.354858384512338</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.01256431403903945</v>
+        <v>0.01209896907463058</v>
       </c>
       <c r="W28">
-        <v>0.2328373347495945</v>
+        <v>0.2329470630922021</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.04869889162418395</v>
+        <v>0.04689522897143639</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1391554257109451</v>
+        <v>0.1410554257109451</v>
       </c>
       <c r="C29">
-        <v>20.70850300872096</v>
+        <v>19.76202055723692</v>
       </c>
       <c r="D29">
-        <v>32.64780300872096</v>
+        <v>32.23722055723692</v>
       </c>
       <c r="E29">
-        <v>4.579300000000002</v>
+        <v>5.115200000000002</v>
       </c>
       <c r="F29">
-        <v>14.4693</v>
+        <v>15.0052</v>
       </c>
       <c r="G29">
         <v>2.53</v>
@@ -3790,37 +3790,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M29">
-        <v>3.411860940000001</v>
+        <v>3.538226160000001</v>
       </c>
       <c r="N29">
-        <v>-3.251860940000001</v>
+        <v>-3.378226160000001</v>
       </c>
       <c r="O29">
-        <v>-0.8389801225200002</v>
+        <v>-0.8715823492800001</v>
       </c>
       <c r="P29">
-        <v>-2.41288081748</v>
+        <v>-2.50664381072</v>
       </c>
       <c r="Q29">
-        <v>3.017119182519999</v>
+        <v>2.923356189279999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1044653680493842</v>
+        <v>0.1052801648278479</v>
       </c>
       <c r="T29">
-        <v>1.354858384512338</v>
+        <v>1.37367586207501</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.01209896907463058</v>
+        <v>0.01166686303625092</v>
       </c>
       <c r="W29">
-        <v>0.2329470630922021</v>
+        <v>0.2330489536960521</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.04689522897143639</v>
+        <v>0.04522039936531363</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1410554257109451</v>
+        <v>0.1429554257109451</v>
       </c>
       <c r="C30">
-        <v>19.76202055723692</v>
+        <v>18.82573690688124</v>
       </c>
       <c r="D30">
-        <v>32.23722055723692</v>
+        <v>31.83683690688125</v>
       </c>
       <c r="E30">
-        <v>5.115200000000002</v>
+        <v>5.651100000000003</v>
       </c>
       <c r="F30">
-        <v>15.0052</v>
+        <v>15.5411</v>
       </c>
       <c r="G30">
         <v>2.53</v>
@@ -3872,37 +3872,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M30">
-        <v>3.538226160000001</v>
+        <v>3.664591380000001</v>
       </c>
       <c r="N30">
-        <v>-3.378226160000001</v>
+        <v>-3.504591380000001</v>
       </c>
       <c r="O30">
-        <v>-0.8715823492800001</v>
+        <v>-0.9041845760400002</v>
       </c>
       <c r="P30">
-        <v>-2.50664381072</v>
+        <v>-2.60040680396</v>
       </c>
       <c r="Q30">
-        <v>2.923356189279999</v>
+        <v>2.829593196039999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1052801648278479</v>
+        <v>0.1061179136282401</v>
       </c>
       <c r="T30">
-        <v>1.37367586207501</v>
+        <v>1.393023409428179</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.01166686303625092</v>
+        <v>0.01126455741431123</v>
       </c>
       <c r="W30">
-        <v>0.2330489536960521</v>
+        <v>0.2331438173617054</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.04522039936531363</v>
+        <v>0.04366107524926832</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.142955425710945</v>
+        <v>0.1448554257109451</v>
       </c>
       <c r="C31">
-        <v>18.82573690688125</v>
+        <v>17.89927671454978</v>
       </c>
       <c r="D31">
-        <v>31.83683690688125</v>
+        <v>31.44627671454978</v>
       </c>
       <c r="E31">
-        <v>5.6511</v>
+        <v>6.187000000000001</v>
       </c>
       <c r="F31">
-        <v>15.5411</v>
+        <v>16.077</v>
       </c>
       <c r="G31">
         <v>2.53</v>
@@ -3954,37 +3954,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M31">
-        <v>3.66459138</v>
+        <v>3.7909566</v>
       </c>
       <c r="N31">
-        <v>-3.50459138</v>
+        <v>-3.6309566</v>
       </c>
       <c r="O31">
-        <v>-0.90418457604</v>
+        <v>-0.9367868028</v>
       </c>
       <c r="P31">
-        <v>-2.60040680396</v>
+        <v>-2.6941697972</v>
       </c>
       <c r="Q31">
-        <v>2.82959319604</v>
+        <v>2.735830202799999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1061179136282401</v>
+        <v>0.1069795981086436</v>
       </c>
       <c r="T31">
-        <v>1.393023409428179</v>
+        <v>1.412923743848581</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.01126455741431123</v>
+        <v>0.01088907216716753</v>
       </c>
       <c r="W31">
-        <v>0.2331438173617054</v>
+        <v>0.2332323567829819</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.04366107524926832</v>
+        <v>0.04220570607429275</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1448554257109451</v>
+        <v>0.1467554257109451</v>
       </c>
       <c r="C32">
-        <v>17.89927671454978</v>
+        <v>16.98228283210145</v>
       </c>
       <c r="D32">
-        <v>31.44627671454978</v>
+        <v>31.06518283210145</v>
       </c>
       <c r="E32">
-        <v>6.187000000000001</v>
+        <v>6.722899999999999</v>
       </c>
       <c r="F32">
-        <v>16.077</v>
+        <v>16.6129</v>
       </c>
       <c r="G32">
         <v>2.53</v>
@@ -4036,37 +4036,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M32">
-        <v>3.7909566</v>
+        <v>3.91732182</v>
       </c>
       <c r="N32">
-        <v>-3.6309566</v>
+        <v>-3.75732182</v>
       </c>
       <c r="O32">
-        <v>-0.9367868028</v>
+        <v>-0.9693890295600001</v>
       </c>
       <c r="P32">
-        <v>-2.6941697972</v>
+        <v>-2.78793279044</v>
       </c>
       <c r="Q32">
-        <v>2.735830202799999</v>
+        <v>2.64206720956</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1069795981086436</v>
+        <v>0.1078662589507978</v>
       </c>
       <c r="T32">
-        <v>1.412923743848581</v>
+        <v>1.433400899556532</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.01088907216716753</v>
+        <v>0.01053781177467825</v>
       </c>
       <c r="W32">
-        <v>0.2332323567829819</v>
+        <v>0.2333151839835309</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.04220570607429275</v>
+        <v>0.04084423168479945</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1467554257109451</v>
+        <v>0.1486554257109451</v>
       </c>
       <c r="C33">
-        <v>16.98228283210145</v>
+        <v>16.07441521704595</v>
       </c>
       <c r="D33">
-        <v>31.06518283210145</v>
+        <v>30.69321521704596</v>
       </c>
       <c r="E33">
-        <v>6.722899999999999</v>
+        <v>7.258800000000001</v>
       </c>
       <c r="F33">
-        <v>16.6129</v>
+        <v>17.1488</v>
       </c>
       <c r="G33">
         <v>2.53</v>
@@ -4118,37 +4118,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M33">
-        <v>3.91732182</v>
+        <v>4.043687040000001</v>
       </c>
       <c r="N33">
-        <v>-3.75732182</v>
+        <v>-3.883687040000001</v>
       </c>
       <c r="O33">
-        <v>-0.9693890295600001</v>
+        <v>-1.00199125632</v>
       </c>
       <c r="P33">
-        <v>-2.78793279044</v>
+        <v>-2.881695783680001</v>
       </c>
       <c r="Q33">
-        <v>2.64206720956</v>
+        <v>2.548304216319999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1078662589507978</v>
+        <v>0.1087789980530154</v>
       </c>
       <c r="T33">
-        <v>1.433400899556532</v>
+        <v>1.45448032455001</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.01053781177467825</v>
+        <v>0.01020850515671955</v>
       </c>
       <c r="W33">
-        <v>0.2333151839835309</v>
+        <v>0.2333928344840455</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.04084423168479945</v>
+        <v>0.03956784944464942</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1486554257109451</v>
+        <v>0.150555425710945</v>
       </c>
       <c r="C34">
-        <v>16.07441521704595</v>
+        <v>15.17534992056465</v>
       </c>
       <c r="D34">
-        <v>30.69321521704596</v>
+        <v>30.33004992056465</v>
       </c>
       <c r="E34">
-        <v>7.258800000000001</v>
+        <v>7.794700000000002</v>
       </c>
       <c r="F34">
-        <v>17.1488</v>
+        <v>17.6847</v>
       </c>
       <c r="G34">
         <v>2.53</v>
@@ -4200,37 +4200,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M34">
-        <v>4.043687040000001</v>
+        <v>4.170052260000001</v>
       </c>
       <c r="N34">
-        <v>-3.883687040000001</v>
+        <v>-4.010052260000001</v>
       </c>
       <c r="O34">
-        <v>-1.00199125632</v>
+        <v>-1.03459348308</v>
       </c>
       <c r="P34">
-        <v>-2.881695783680001</v>
+        <v>-2.975458776920001</v>
       </c>
       <c r="Q34">
-        <v>2.548304216319999</v>
+        <v>2.454541223079999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1087789980530154</v>
+        <v>0.1097189830985828</v>
       </c>
       <c r="T34">
-        <v>1.45448032455001</v>
+        <v>1.476188986110458</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.01020850515671955</v>
+        <v>0.009899156515606839</v>
       </c>
       <c r="W34">
-        <v>0.2333928344840455</v>
+        <v>0.2334657788936199</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.03956784944464942</v>
+        <v>0.03836882370390249</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.150555425710945</v>
+        <v>0.1524554257109451</v>
       </c>
       <c r="C35">
-        <v>15.17534992056465</v>
+        <v>14.28477814653426</v>
       </c>
       <c r="D35">
-        <v>30.33004992056465</v>
+        <v>29.97537814653426</v>
       </c>
       <c r="E35">
-        <v>7.794700000000002</v>
+        <v>8.3306</v>
       </c>
       <c r="F35">
-        <v>17.6847</v>
+        <v>18.2206</v>
       </c>
       <c r="G35">
         <v>2.53</v>
@@ -4282,37 +4282,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M35">
-        <v>4.170052260000001</v>
+        <v>4.296417480000001</v>
       </c>
       <c r="N35">
-        <v>-4.010052260000001</v>
+        <v>-4.13641748</v>
       </c>
       <c r="O35">
-        <v>-1.03459348308</v>
+        <v>-1.06719570984</v>
       </c>
       <c r="P35">
-        <v>-2.975458776920001</v>
+        <v>-3.06922177016</v>
       </c>
       <c r="Q35">
-        <v>2.454541223079999</v>
+        <v>2.360778229839999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1097189830985828</v>
+        <v>0.1106874525394705</v>
       </c>
       <c r="T35">
-        <v>1.476188986110458</v>
+        <v>1.498555485900011</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.009899156515606839</v>
+        <v>0.009608004853383111</v>
       </c>
       <c r="W35">
-        <v>0.2334657788936199</v>
+        <v>0.2335344324555723</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.03836882370390249</v>
+        <v>0.0372403288890818</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1524554257109451</v>
+        <v>0.1543554257109451</v>
       </c>
       <c r="C36">
-        <v>14.28477814653426</v>
+        <v>13.40240537580891</v>
       </c>
       <c r="D36">
-        <v>29.97537814653426</v>
+        <v>29.62890537580892</v>
       </c>
       <c r="E36">
-        <v>8.3306</v>
+        <v>8.866500000000002</v>
       </c>
       <c r="F36">
-        <v>18.2206</v>
+        <v>18.7565</v>
       </c>
       <c r="G36">
         <v>2.53</v>
@@ -4364,37 +4364,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M36">
-        <v>4.296417480000001</v>
+        <v>4.422782700000001</v>
       </c>
       <c r="N36">
-        <v>-4.13641748</v>
+        <v>-4.262782700000001</v>
       </c>
       <c r="O36">
-        <v>-1.06719570984</v>
+        <v>-1.0997979366</v>
       </c>
       <c r="P36">
-        <v>-3.06922177016</v>
+        <v>-3.162984763400001</v>
       </c>
       <c r="Q36">
-        <v>2.360778229839999</v>
+        <v>2.267015236599999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1106874525394705</v>
+        <v>0.1116857210400777</v>
       </c>
       <c r="T36">
-        <v>1.498555485900011</v>
+        <v>1.521610185683088</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.009608004853383111</v>
+        <v>0.009333490429000736</v>
       </c>
       <c r="W36">
-        <v>0.2335344324555723</v>
+        <v>0.2335991629568416</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.0372403288890818</v>
+        <v>0.03617631949225086</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1543554257109451</v>
+        <v>0.1562554257109451</v>
       </c>
       <c r="C37">
-        <v>13.40240537580891</v>
+        <v>12.52795055054023</v>
       </c>
       <c r="D37">
-        <v>29.62890537580892</v>
+        <v>29.29035055054023</v>
       </c>
       <c r="E37">
-        <v>8.866500000000002</v>
+        <v>9.402400000000004</v>
       </c>
       <c r="F37">
-        <v>18.7565</v>
+        <v>19.2924</v>
       </c>
       <c r="G37">
         <v>2.53</v>
@@ -4446,37 +4446,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M37">
-        <v>4.422782700000001</v>
+        <v>4.549147920000001</v>
       </c>
       <c r="N37">
-        <v>-4.262782700000001</v>
+        <v>-4.389147920000001</v>
       </c>
       <c r="O37">
-        <v>-1.0997979366</v>
+        <v>-1.13240016336</v>
       </c>
       <c r="P37">
-        <v>-3.162984763400001</v>
+        <v>-3.256747756640001</v>
       </c>
       <c r="Q37">
-        <v>2.267015236599999</v>
+        <v>2.173252243359999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1116857210400777</v>
+        <v>0.1127151854313289</v>
       </c>
       <c r="T37">
-        <v>1.521610185683088</v>
+        <v>1.545385344834386</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.009333490429000736</v>
+        <v>0.009074226805972935</v>
       </c>
       <c r="W37">
-        <v>0.2335991629568416</v>
+        <v>0.2336602973191516</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.03617631949225086</v>
+        <v>0.03517142172857723</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1562554257109451</v>
+        <v>0.1581554257109451</v>
       </c>
       <c r="C38">
-        <v>12.52795055054023</v>
+        <v>11.66114531378815</v>
       </c>
       <c r="D38">
-        <v>29.29035055054023</v>
+        <v>28.95944531378815</v>
       </c>
       <c r="E38">
-        <v>9.4024</v>
+        <v>9.938300000000002</v>
       </c>
       <c r="F38">
-        <v>19.2924</v>
+        <v>19.8283</v>
       </c>
       <c r="G38">
         <v>2.53</v>
@@ -4528,37 +4528,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M38">
-        <v>4.54914792</v>
+        <v>4.675513140000001</v>
       </c>
       <c r="N38">
-        <v>-4.38914792</v>
+        <v>-4.51551314</v>
       </c>
       <c r="O38">
-        <v>-1.13240016336</v>
+        <v>-1.16500239012</v>
       </c>
       <c r="P38">
-        <v>-3.25674775664</v>
+        <v>-3.35051074988</v>
       </c>
       <c r="Q38">
-        <v>2.173252243359999</v>
+        <v>2.07948925012</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1127151854313289</v>
+        <v>0.1137773312318262</v>
       </c>
       <c r="T38">
-        <v>1.545385344834386</v>
+        <v>1.569915270942868</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.009074226805972937</v>
+        <v>0.008828977432838534</v>
       </c>
       <c r="W38">
-        <v>0.2336602973191516</v>
+        <v>0.2337181271213367</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.03517142172857723</v>
+        <v>0.03422084276294002</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1581554257109451</v>
+        <v>0.1600554257109451</v>
       </c>
       <c r="C39">
-        <v>11.66114531378815</v>
+        <v>10.80173330009832</v>
       </c>
       <c r="D39">
-        <v>28.95944531378815</v>
+        <v>28.63593330009832</v>
       </c>
       <c r="E39">
-        <v>9.938300000000002</v>
+        <v>10.4742</v>
       </c>
       <c r="F39">
-        <v>19.8283</v>
+        <v>20.3642</v>
       </c>
       <c r="G39">
         <v>2.53</v>
@@ -4610,37 +4610,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M39">
-        <v>4.675513140000001</v>
+        <v>4.80187836</v>
       </c>
       <c r="N39">
-        <v>-4.51551314</v>
+        <v>-4.64187836</v>
       </c>
       <c r="O39">
-        <v>-1.16500239012</v>
+        <v>-1.19760461688</v>
       </c>
       <c r="P39">
-        <v>-3.35051074988</v>
+        <v>-3.44427374312</v>
       </c>
       <c r="Q39">
-        <v>2.07948925012</v>
+        <v>1.98572625688</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1137773312318262</v>
+        <v>0.1148737398000814</v>
       </c>
       <c r="T39">
-        <v>1.569915270942868</v>
+        <v>1.595236484990334</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.008828977432838534</v>
+        <v>0.008596635921448048</v>
       </c>
       <c r="W39">
-        <v>0.2337181271213367</v>
+        <v>0.2337729132497226</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.03422084276294002</v>
+        <v>0.03332029426917849</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1600554257109451</v>
+        <v>0.1619554257109451</v>
       </c>
       <c r="C40">
-        <v>10.80173330009832</v>
+        <v>9.949469473105022</v>
       </c>
       <c r="D40">
-        <v>28.63593330009832</v>
+        <v>28.31956947310502</v>
       </c>
       <c r="E40">
-        <v>10.4742</v>
+        <v>11.0101</v>
       </c>
       <c r="F40">
-        <v>20.3642</v>
+        <v>20.9001</v>
       </c>
       <c r="G40">
         <v>2.53</v>
@@ -4692,37 +4692,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M40">
-        <v>4.80187836</v>
+        <v>4.928243580000001</v>
       </c>
       <c r="N40">
-        <v>-4.64187836</v>
+        <v>-4.768243580000001</v>
       </c>
       <c r="O40">
-        <v>-1.19760461688</v>
+        <v>-1.23020684364</v>
       </c>
       <c r="P40">
-        <v>-3.44427374312</v>
+        <v>-3.53803673636</v>
       </c>
       <c r="Q40">
-        <v>1.98572625688</v>
+        <v>1.891963263639999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1148737398000814</v>
+        <v>0.1160060961902467</v>
       </c>
       <c r="T40">
-        <v>1.595236484990334</v>
+        <v>1.62138790277706</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.008596635921448048</v>
+        <v>0.008376209359359635</v>
       </c>
       <c r="W40">
-        <v>0.2337729132497226</v>
+        <v>0.233824889833063</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.03332029426917849</v>
+        <v>0.03246592774945589</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1619554257109451</v>
+        <v>0.1638554257109451</v>
       </c>
       <c r="C41">
-        <v>9.949469473105022</v>
+        <v>9.104119506562274</v>
       </c>
       <c r="D41">
-        <v>28.31956947310502</v>
+        <v>28.01011950656228</v>
       </c>
       <c r="E41">
-        <v>11.0101</v>
+        <v>11.546</v>
       </c>
       <c r="F41">
-        <v>20.9001</v>
+        <v>21.436</v>
       </c>
       <c r="G41">
         <v>2.53</v>
@@ -4774,37 +4774,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M41">
-        <v>4.928243580000001</v>
+        <v>5.054608800000001</v>
       </c>
       <c r="N41">
-        <v>-4.768243580000001</v>
+        <v>-4.894608800000001</v>
       </c>
       <c r="O41">
-        <v>-1.23020684364</v>
+        <v>-1.2628090704</v>
       </c>
       <c r="P41">
-        <v>-3.53803673636</v>
+        <v>-3.631799729600001</v>
       </c>
       <c r="Q41">
-        <v>1.891963263639999</v>
+        <v>1.798200270399999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1160060961902467</v>
+        <v>0.1171761977934175</v>
       </c>
       <c r="T41">
-        <v>1.62138790277706</v>
+        <v>1.648411034490011</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.008376209359359635</v>
+        <v>0.008166804125375644</v>
       </c>
       <c r="W41">
-        <v>0.233824889833063</v>
+        <v>0.2338742675872365</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.03246592774945589</v>
+        <v>0.03165427955571953</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1638554257109451</v>
+        <v>0.1657554257109451</v>
       </c>
       <c r="C42">
-        <v>9.104119506562274</v>
+        <v>8.265459205517523</v>
       </c>
       <c r="D42">
-        <v>28.01011950656228</v>
+        <v>27.70735920551752</v>
       </c>
       <c r="E42">
-        <v>11.546</v>
+        <v>12.0819</v>
       </c>
       <c r="F42">
-        <v>21.436</v>
+        <v>21.9719</v>
       </c>
       <c r="G42">
         <v>2.53</v>
@@ -4856,37 +4856,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M42">
-        <v>5.054608800000001</v>
+        <v>5.180974020000001</v>
       </c>
       <c r="N42">
-        <v>-4.894608800000001</v>
+        <v>-5.020974020000001</v>
       </c>
       <c r="O42">
-        <v>-1.2628090704</v>
+        <v>-1.29541129716</v>
       </c>
       <c r="P42">
-        <v>-3.631799729600001</v>
+        <v>-3.72556272284</v>
       </c>
       <c r="Q42">
-        <v>1.798200270399999</v>
+        <v>1.704437277159999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1171761977934175</v>
+        <v>0.1183859638577127</v>
       </c>
       <c r="T42">
-        <v>1.648411034490011</v>
+        <v>1.676350204566113</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.008166804125375644</v>
+        <v>0.007967613780854286</v>
       </c>
       <c r="W42">
-        <v>0.2338742675872365</v>
+        <v>0.2339212366704746</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.03165427955571953</v>
+        <v>0.03088222395679951</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1657554257109451</v>
+        <v>0.1676554257109451</v>
       </c>
       <c r="C43">
-        <v>8.265459205517523</v>
+        <v>7.433273964622884</v>
       </c>
       <c r="D43">
-        <v>27.70735920551752</v>
+        <v>27.41107396462289</v>
       </c>
       <c r="E43">
-        <v>12.0819</v>
+        <v>12.6178</v>
       </c>
       <c r="F43">
-        <v>21.9719</v>
+        <v>22.5078</v>
       </c>
       <c r="G43">
         <v>2.53</v>
@@ -4938,37 +4938,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M43">
-        <v>5.180974020000001</v>
+        <v>5.307339240000001</v>
       </c>
       <c r="N43">
-        <v>-5.020974020000001</v>
+        <v>-5.147339240000001</v>
       </c>
       <c r="O43">
-        <v>-1.29541129716</v>
+        <v>-1.32801352392</v>
       </c>
       <c r="P43">
-        <v>-3.72556272284</v>
+        <v>-3.819325716080001</v>
       </c>
       <c r="Q43">
-        <v>1.704437277159999</v>
+        <v>1.610674283919999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1183859638577127</v>
+        <v>0.1196374459931905</v>
       </c>
       <c r="T43">
-        <v>1.676350204566113</v>
+        <v>1.705252794300012</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.007967613780854286</v>
+        <v>0.007777908690833947</v>
       </c>
       <c r="W43">
-        <v>0.2339212366704746</v>
+        <v>0.2339659691307014</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.03088222395679951</v>
+        <v>0.03014693291020909</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.167655425710945</v>
+        <v>0.1695554257109451</v>
       </c>
       <c r="C44">
-        <v>7.433273964622895</v>
+        <v>6.607358260833685</v>
       </c>
       <c r="D44">
-        <v>27.41107396462289</v>
+        <v>27.12105826083368</v>
       </c>
       <c r="E44">
-        <v>12.6178</v>
+        <v>13.1537</v>
       </c>
       <c r="F44">
-        <v>22.5078</v>
+        <v>23.0437</v>
       </c>
       <c r="G44">
         <v>2.53</v>
@@ -5020,37 +5020,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M44">
-        <v>5.30733924</v>
+        <v>5.43370446</v>
       </c>
       <c r="N44">
-        <v>-5.14733924</v>
+        <v>-5.27370446</v>
       </c>
       <c r="O44">
-        <v>-1.32801352392</v>
+        <v>-1.36061575068</v>
       </c>
       <c r="P44">
-        <v>-3.81932571608</v>
+        <v>-3.91308870932</v>
       </c>
       <c r="Q44">
-        <v>1.61067428392</v>
+        <v>1.51691129068</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1196374459931905</v>
+        <v>0.1209328397825447</v>
       </c>
       <c r="T44">
-        <v>1.705252794300012</v>
+        <v>1.735169509989485</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.007777908690833947</v>
+        <v>0.007597027093372693</v>
       </c>
       <c r="W44">
-        <v>0.2339659691307014</v>
+        <v>0.2340086210113827</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.03014693291020909</v>
+        <v>0.02944584144718099</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1695554257109451</v>
+        <v>0.1714554257109451</v>
       </c>
       <c r="C45">
-        <v>6.607358260833685</v>
+        <v>5.787515177973912</v>
       </c>
       <c r="D45">
-        <v>27.12105826083368</v>
+        <v>26.83711517797391</v>
       </c>
       <c r="E45">
-        <v>13.1537</v>
+        <v>13.6896</v>
       </c>
       <c r="F45">
-        <v>23.0437</v>
+        <v>23.5796</v>
       </c>
       <c r="G45">
         <v>2.53</v>
@@ -5102,37 +5102,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M45">
-        <v>5.43370446</v>
+        <v>5.560069680000001</v>
       </c>
       <c r="N45">
-        <v>-5.27370446</v>
+        <v>-5.400069680000001</v>
       </c>
       <c r="O45">
-        <v>-1.36061575068</v>
+        <v>-1.39321797744</v>
       </c>
       <c r="P45">
-        <v>-3.91308870932</v>
+        <v>-4.006851702560001</v>
       </c>
       <c r="Q45">
-        <v>1.51691129068</v>
+        <v>1.423148297439999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1209328397825447</v>
+        <v>0.1222744976358044</v>
       </c>
       <c r="T45">
-        <v>1.735169509989485</v>
+        <v>1.766154679810727</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.007597027093372693</v>
+        <v>0.007424367386705131</v>
       </c>
       <c r="W45">
-        <v>0.2340086210113827</v>
+        <v>0.2340493341702149</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.02944584144718099</v>
+        <v>0.02877661777792684</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1714554257109451</v>
+        <v>0.1733554257109451</v>
       </c>
       <c r="C46">
-        <v>5.787515177973912</v>
+        <v>4.973555960857681</v>
       </c>
       <c r="D46">
-        <v>26.83711517797391</v>
+        <v>26.55905596085768</v>
       </c>
       <c r="E46">
-        <v>13.6896</v>
+        <v>14.2255</v>
       </c>
       <c r="F46">
-        <v>23.5796</v>
+        <v>24.1155</v>
       </c>
       <c r="G46">
         <v>2.53</v>
@@ -5184,37 +5184,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M46">
-        <v>5.560069680000001</v>
+        <v>5.6864349</v>
       </c>
       <c r="N46">
-        <v>-5.400069680000001</v>
+        <v>-5.5264349</v>
       </c>
       <c r="O46">
-        <v>-1.39321797744</v>
+        <v>-1.4258202042</v>
       </c>
       <c r="P46">
-        <v>-4.006851702560001</v>
+        <v>-4.1006146958</v>
       </c>
       <c r="Q46">
-        <v>1.423148297439999</v>
+        <v>1.3293853042</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1222744976358044</v>
+        <v>0.1236649430473645</v>
       </c>
       <c r="T46">
-        <v>1.766154679810727</v>
+        <v>1.798266583080012</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.007424367386705131</v>
+        <v>0.007259381444778351</v>
       </c>
       <c r="W46">
-        <v>0.2340493341702149</v>
+        <v>0.2340882378553213</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.02877661777792684</v>
+        <v>0.02813713738286183</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1733554257109451</v>
+        <v>0.1752554257109451</v>
       </c>
       <c r="C47">
-        <v>4.973555960857681</v>
+        <v>4.1652995968448</v>
       </c>
       <c r="D47">
-        <v>26.55905596085768</v>
+        <v>26.2866995968448</v>
       </c>
       <c r="E47">
-        <v>14.2255</v>
+        <v>14.7614</v>
       </c>
       <c r="F47">
-        <v>24.1155</v>
+        <v>24.6514</v>
       </c>
       <c r="G47">
         <v>2.53</v>
@@ -5266,37 +5266,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M47">
-        <v>5.6864349</v>
+        <v>5.812800120000001</v>
       </c>
       <c r="N47">
-        <v>-5.5264349</v>
+        <v>-5.652800120000001</v>
       </c>
       <c r="O47">
-        <v>-1.4258202042</v>
+        <v>-1.45842243096</v>
       </c>
       <c r="P47">
-        <v>-4.1006146958</v>
+        <v>-4.194377689040001</v>
       </c>
       <c r="Q47">
-        <v>1.3293853042</v>
+        <v>1.235622310959998</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1236649430473645</v>
+        <v>0.1251068864371306</v>
       </c>
       <c r="T47">
-        <v>1.798266583080012</v>
+        <v>1.831567816100013</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.007259381444778351</v>
+        <v>0.007101568804674472</v>
       </c>
       <c r="W47">
-        <v>0.2340882378553213</v>
+        <v>0.2341254500758577</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.02813713738286183</v>
+        <v>0.02752546048323434</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1752554257109451</v>
+        <v>0.1771554257109451</v>
       </c>
       <c r="C48">
-        <v>4.1652995968448</v>
+        <v>3.36257242288125</v>
       </c>
       <c r="D48">
-        <v>26.2866995968448</v>
+        <v>26.01987242288125</v>
       </c>
       <c r="E48">
-        <v>14.7614</v>
+        <v>15.2973</v>
       </c>
       <c r="F48">
-        <v>24.6514</v>
+        <v>25.1873</v>
       </c>
       <c r="G48">
         <v>2.53</v>
@@ -5348,37 +5348,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M48">
-        <v>5.812800120000001</v>
+        <v>5.939165340000002</v>
       </c>
       <c r="N48">
-        <v>-5.652800120000001</v>
+        <v>-5.779165340000001</v>
       </c>
       <c r="O48">
-        <v>-1.45842243096</v>
+        <v>-1.49102465772</v>
       </c>
       <c r="P48">
-        <v>-4.194377689040001</v>
+        <v>-4.288140682280001</v>
       </c>
       <c r="Q48">
-        <v>1.235622310959998</v>
+        <v>1.141859317719999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1251068864371306</v>
+        <v>0.1266032427850009</v>
       </c>
       <c r="T48">
-        <v>1.831567816100013</v>
+        <v>1.866125699422654</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.007101568804674472</v>
+        <v>0.006950471596064377</v>
       </c>
       <c r="W48">
-        <v>0.2341254500758577</v>
+        <v>0.2341610787976481</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.02752546048323434</v>
+        <v>0.02693981238784637</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1771554257109451</v>
+        <v>0.1790554257109451</v>
       </c>
       <c r="C49">
-        <v>3.36257242288125</v>
+        <v>2.565207756232088</v>
       </c>
       <c r="D49">
-        <v>26.01987242288125</v>
+        <v>25.75840775623209</v>
       </c>
       <c r="E49">
-        <v>15.2973</v>
+        <v>15.8332</v>
       </c>
       <c r="F49">
-        <v>25.1873</v>
+        <v>25.7232</v>
       </c>
       <c r="G49">
         <v>2.53</v>
@@ -5430,37 +5430,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M49">
-        <v>5.939165340000002</v>
+        <v>6.065530560000001</v>
       </c>
       <c r="N49">
-        <v>-5.779165340000001</v>
+        <v>-5.905530560000001</v>
       </c>
       <c r="O49">
-        <v>-1.49102465772</v>
+        <v>-1.52362688448</v>
       </c>
       <c r="P49">
-        <v>-4.288140682280001</v>
+        <v>-4.38190367552</v>
       </c>
       <c r="Q49">
-        <v>1.141859317719999</v>
+        <v>1.048096324479999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1266032427850009</v>
+        <v>0.1281571513000971</v>
       </c>
       <c r="T49">
-        <v>1.866125699422654</v>
+        <v>1.902012732103859</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.006950471596064377</v>
+        <v>0.006805670104479703</v>
       </c>
       <c r="W49">
-        <v>0.2341610787976481</v>
+        <v>0.2341952229893637</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.02693981238784637</v>
+        <v>0.02637856629643298</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1790554257109451</v>
+        <v>0.1809554257109451</v>
       </c>
       <c r="C50">
-        <v>2.565207756232088</v>
+        <v>1.773045547256441</v>
       </c>
       <c r="D50">
-        <v>25.75840775623209</v>
+        <v>25.50214554725644</v>
       </c>
       <c r="E50">
-        <v>15.8332</v>
+        <v>16.3691</v>
       </c>
       <c r="F50">
-        <v>25.7232</v>
+        <v>26.2591</v>
       </c>
       <c r="G50">
         <v>2.53</v>
@@ -5512,37 +5512,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M50">
-        <v>6.065530560000001</v>
+        <v>6.19189578</v>
       </c>
       <c r="N50">
-        <v>-5.905530560000001</v>
+        <v>-6.03189578</v>
       </c>
       <c r="O50">
-        <v>-1.52362688448</v>
+        <v>-1.55622911124</v>
       </c>
       <c r="P50">
-        <v>-4.38190367552</v>
+        <v>-4.47566666876</v>
       </c>
       <c r="Q50">
-        <v>1.048096324479999</v>
+        <v>0.95433333124</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1281571513000971</v>
+        <v>0.1297719974040206</v>
       </c>
       <c r="T50">
-        <v>1.902012732103859</v>
+        <v>1.939307099400013</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.006805670104479703</v>
+        <v>0.006666778877857669</v>
       </c>
       <c r="W50">
-        <v>0.2341952229893637</v>
+        <v>0.2342279735406012</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.02637856629643298</v>
+        <v>0.02584022820875065</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1809554257109451</v>
+        <v>0.1828554257109451</v>
       </c>
       <c r="C51">
-        <v>1.773045547256441</v>
+        <v>0.9859320527051487</v>
       </c>
       <c r="D51">
-        <v>25.50214554725644</v>
+        <v>25.25093205270515</v>
       </c>
       <c r="E51">
-        <v>16.3691</v>
+        <v>16.905</v>
       </c>
       <c r="F51">
-        <v>26.2591</v>
+        <v>26.795</v>
       </c>
       <c r="G51">
         <v>2.53</v>
@@ -5594,37 +5594,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M51">
-        <v>6.19189578</v>
+        <v>6.318261000000001</v>
       </c>
       <c r="N51">
-        <v>-6.03189578</v>
+        <v>-6.158261</v>
       </c>
       <c r="O51">
-        <v>-1.55622911124</v>
+        <v>-1.588831338</v>
       </c>
       <c r="P51">
-        <v>-4.47566666876</v>
+        <v>-4.569429662</v>
       </c>
       <c r="Q51">
-        <v>0.95433333124</v>
+        <v>0.8605703379999996</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1297719974040206</v>
+        <v>0.131451437352101</v>
       </c>
       <c r="T51">
-        <v>1.939307099400013</v>
+        <v>1.978093241388013</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.006666778877857669</v>
+        <v>0.006533443300300515</v>
       </c>
       <c r="W51">
-        <v>0.2342279735406012</v>
+        <v>0.2342594140697891</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.02584022820875065</v>
+        <v>0.02532342364457563</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1828554257109451</v>
+        <v>0.1847554257109451</v>
       </c>
       <c r="C52">
-        <v>0.9859320527051487</v>
+        <v>0.203719528139338</v>
       </c>
       <c r="D52">
-        <v>25.25093205270515</v>
+        <v>25.00461952813934</v>
       </c>
       <c r="E52">
-        <v>16.905</v>
+        <v>17.4409</v>
       </c>
       <c r="F52">
-        <v>26.795</v>
+        <v>27.3309</v>
       </c>
       <c r="G52">
         <v>2.53</v>
@@ -5676,37 +5676,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M52">
-        <v>6.318261000000001</v>
+        <v>6.444626220000001</v>
       </c>
       <c r="N52">
-        <v>-6.158261</v>
+        <v>-6.284626220000001</v>
       </c>
       <c r="O52">
-        <v>-1.588831338</v>
+        <v>-1.62143356476</v>
       </c>
       <c r="P52">
-        <v>-4.569429662</v>
+        <v>-4.66319265524</v>
       </c>
       <c r="Q52">
-        <v>0.8605703379999996</v>
+        <v>0.7668073447599992</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.131451437352101</v>
+        <v>0.1331994258694908</v>
       </c>
       <c r="T52">
-        <v>1.978093241388013</v>
+        <v>2.018462491212259</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.006533443300300515</v>
+        <v>0.006405336568922074</v>
       </c>
       <c r="W52">
-        <v>0.2342594140697891</v>
+        <v>0.2342896216370482</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.02532342364457563</v>
+        <v>0.02482688592605453</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1847554257109451</v>
+        <v>0.1866554257109451</v>
       </c>
       <c r="C53">
-        <v>0.203719528139338</v>
+        <v>-0.5737340618228401</v>
       </c>
       <c r="D53">
-        <v>25.00461952813934</v>
+        <v>24.76306593817716</v>
       </c>
       <c r="E53">
-        <v>17.4409</v>
+        <v>17.9768</v>
       </c>
       <c r="F53">
-        <v>27.3309</v>
+        <v>27.8668</v>
       </c>
       <c r="G53">
         <v>2.53</v>
@@ -5758,37 +5758,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M53">
-        <v>6.444626220000001</v>
+        <v>6.57099144</v>
       </c>
       <c r="N53">
-        <v>-6.284626220000001</v>
+        <v>-6.41099144</v>
       </c>
       <c r="O53">
-        <v>-1.62143356476</v>
+        <v>-1.65403579152</v>
       </c>
       <c r="P53">
-        <v>-4.66319265524</v>
+        <v>-4.75695564848</v>
       </c>
       <c r="Q53">
-        <v>0.7668073447599992</v>
+        <v>0.6730443515199998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1331994258694908</v>
+        <v>0.1350202472417719</v>
       </c>
       <c r="T53">
-        <v>2.018462491212259</v>
+        <v>2.060513793112514</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.006405336568922074</v>
+        <v>0.006282157019519727</v>
       </c>
       <c r="W53">
-        <v>0.2342896216370482</v>
+        <v>0.2343186673747973</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.02482688592605453</v>
+        <v>0.02434944581209197</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1866554257109451</v>
+        <v>0.1885554257109451</v>
       </c>
       <c r="C54">
-        <v>-0.5737340618228401</v>
+        <v>-1.346565316625494</v>
       </c>
       <c r="D54">
-        <v>24.76306593817716</v>
+        <v>24.52613468337451</v>
       </c>
       <c r="E54">
-        <v>17.9768</v>
+        <v>18.5127</v>
       </c>
       <c r="F54">
-        <v>27.8668</v>
+        <v>28.4027</v>
       </c>
       <c r="G54">
         <v>2.53</v>
@@ -5840,37 +5840,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M54">
-        <v>6.57099144</v>
+        <v>6.697356660000001</v>
       </c>
       <c r="N54">
-        <v>-6.41099144</v>
+        <v>-6.537356660000001</v>
       </c>
       <c r="O54">
-        <v>-1.65403579152</v>
+        <v>-1.68663801828</v>
       </c>
       <c r="P54">
-        <v>-4.75695564848</v>
+        <v>-4.850718641720001</v>
       </c>
       <c r="Q54">
-        <v>0.6730443515199998</v>
+        <v>0.5792813582799985</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1350202472417719</v>
+        <v>0.1369185503745755</v>
       </c>
       <c r="T54">
-        <v>2.060513793112514</v>
+        <v>2.104354512114908</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.006282157019519727</v>
+        <v>0.006163625755000486</v>
       </c>
       <c r="W54">
-        <v>0.2343186673747973</v>
+        <v>0.2343466170469709</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.02434944581209197</v>
+        <v>0.02389002230620341</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1885554257109451</v>
+        <v>0.1904554257109451</v>
       </c>
       <c r="C55">
-        <v>-1.346565316625494</v>
+        <v>-2.114905657363725</v>
       </c>
       <c r="D55">
-        <v>24.52613468337451</v>
+        <v>24.29369434263628</v>
       </c>
       <c r="E55">
-        <v>18.5127</v>
+        <v>19.0486</v>
       </c>
       <c r="F55">
-        <v>28.4027</v>
+        <v>28.9386</v>
       </c>
       <c r="G55">
         <v>2.53</v>
@@ -5922,37 +5922,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M55">
-        <v>6.697356660000001</v>
+        <v>6.823721880000002</v>
       </c>
       <c r="N55">
-        <v>-6.537356660000001</v>
+        <v>-6.663721880000002</v>
       </c>
       <c r="O55">
-        <v>-1.68663801828</v>
+        <v>-1.71924024504</v>
       </c>
       <c r="P55">
-        <v>-4.850718641720001</v>
+        <v>-4.944481634960001</v>
       </c>
       <c r="Q55">
-        <v>0.5792813582799985</v>
+        <v>0.485518365039999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1369185503745755</v>
+        <v>0.1388993884261967</v>
       </c>
       <c r="T55">
-        <v>2.104354512114908</v>
+        <v>2.150101349334798</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.006163625755000486</v>
+        <v>0.006049484537315291</v>
       </c>
       <c r="W55">
-        <v>0.2343466170469709</v>
+        <v>0.2343735315461011</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.02389002230620341</v>
+        <v>0.02344761448571819</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1904554257109451</v>
+        <v>0.192355425710945</v>
       </c>
       <c r="C56">
-        <v>-2.114905657363725</v>
+        <v>-2.87888156986244</v>
       </c>
       <c r="D56">
-        <v>24.29369434263628</v>
+        <v>24.06561843013756</v>
       </c>
       <c r="E56">
-        <v>19.0486</v>
+        <v>19.5845</v>
       </c>
       <c r="F56">
-        <v>28.9386</v>
+        <v>29.4745</v>
       </c>
       <c r="G56">
         <v>2.53</v>
@@ -6004,37 +6004,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M56">
-        <v>6.823721880000002</v>
+        <v>6.950087100000001</v>
       </c>
       <c r="N56">
-        <v>-6.663721880000002</v>
+        <v>-6.790087100000001</v>
       </c>
       <c r="O56">
-        <v>-1.71924024504</v>
+        <v>-1.7518424718</v>
       </c>
       <c r="P56">
-        <v>-4.944481634960001</v>
+        <v>-5.038244628200001</v>
       </c>
       <c r="Q56">
-        <v>0.485518365039999</v>
+        <v>0.3917553717999986</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1388993884261967</v>
+        <v>0.1409682637245566</v>
       </c>
       <c r="T56">
-        <v>2.150101349334798</v>
+        <v>2.197881379320015</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.006049484537315291</v>
+        <v>0.005939493909364105</v>
       </c>
       <c r="W56">
-        <v>0.2343735315461011</v>
+        <v>0.234399467336172</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.02344761448571819</v>
+        <v>0.02302129422234145</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.192355425710945</v>
+        <v>0.1942554257109451</v>
       </c>
       <c r="C57">
-        <v>-2.87888156986244</v>
+        <v>-3.638614834190101</v>
       </c>
       <c r="D57">
-        <v>24.06561843013756</v>
+        <v>23.8417851658099</v>
       </c>
       <c r="E57">
-        <v>19.5845</v>
+        <v>20.1204</v>
       </c>
       <c r="F57">
-        <v>29.4745</v>
+        <v>30.0104</v>
       </c>
       <c r="G57">
         <v>2.53</v>
@@ -6086,37 +6086,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M57">
-        <v>6.950087100000001</v>
+        <v>7.076452320000001</v>
       </c>
       <c r="N57">
-        <v>-6.790087100000001</v>
+        <v>-6.916452320000001</v>
       </c>
       <c r="O57">
-        <v>-1.7518424718</v>
+        <v>-1.78444469856</v>
       </c>
       <c r="P57">
-        <v>-5.038244628200001</v>
+        <v>-5.132007621440001</v>
       </c>
       <c r="Q57">
-        <v>0.3917553717999986</v>
+        <v>0.2979923785599992</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1409682637245566</v>
+        <v>0.1431311788092057</v>
       </c>
       <c r="T57">
-        <v>2.197881379320015</v>
+        <v>2.247833228850016</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.005939493909364105</v>
+        <v>0.005833431518125459</v>
       </c>
       <c r="W57">
-        <v>0.234399467336172</v>
+        <v>0.234424476848026</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.02302129422234145</v>
+        <v>0.02261019968265687</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1942554257109451</v>
+        <v>0.1961554257109451</v>
       </c>
       <c r="C58">
-        <v>-3.638614834190101</v>
+        <v>-4.394222741482139</v>
       </c>
       <c r="D58">
-        <v>23.8417851658099</v>
+        <v>23.62207725851787</v>
       </c>
       <c r="E58">
-        <v>20.1204</v>
+        <v>20.65630000000001</v>
       </c>
       <c r="F58">
-        <v>30.0104</v>
+        <v>30.54630000000001</v>
       </c>
       <c r="G58">
         <v>2.53</v>
@@ -6168,37 +6168,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M58">
-        <v>7.076452320000001</v>
+        <v>7.202817540000002</v>
       </c>
       <c r="N58">
-        <v>-6.916452320000001</v>
+        <v>-7.042817540000001</v>
       </c>
       <c r="O58">
-        <v>-1.78444469856</v>
+        <v>-1.81704692532</v>
       </c>
       <c r="P58">
-        <v>-5.132007621440001</v>
+        <v>-5.225770614680001</v>
       </c>
       <c r="Q58">
-        <v>0.2979923785599992</v>
+        <v>0.2042293853199988</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1431311788092057</v>
+        <v>0.1453946945954663</v>
       </c>
       <c r="T58">
-        <v>2.247833228850016</v>
+        <v>2.300108420218621</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.005833431518125459</v>
+        <v>0.005731090614298697</v>
       </c>
       <c r="W58">
-        <v>0.234424476848026</v>
+        <v>0.2344486088331484</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.02261019968265687</v>
+        <v>0.02221352951278566</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1961554257109451</v>
+        <v>0.1980554257109451</v>
       </c>
       <c r="C59">
-        <v>-4.394222741482139</v>
+        <v>-5.145818298885491</v>
       </c>
       <c r="D59">
-        <v>23.62207725851787</v>
+        <v>23.40638170111452</v>
       </c>
       <c r="E59">
-        <v>20.65630000000001</v>
+        <v>21.19220000000001</v>
       </c>
       <c r="F59">
-        <v>30.54630000000001</v>
+        <v>31.08220000000001</v>
       </c>
       <c r="G59">
         <v>2.53</v>
@@ -6250,37 +6250,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M59">
-        <v>7.202817540000002</v>
+        <v>7.329182760000002</v>
       </c>
       <c r="N59">
-        <v>-7.042817540000001</v>
+        <v>-7.169182760000002</v>
       </c>
       <c r="O59">
-        <v>-1.81704692532</v>
+        <v>-1.84964915208</v>
       </c>
       <c r="P59">
-        <v>-5.225770614680001</v>
+        <v>-5.319533607920001</v>
       </c>
       <c r="Q59">
-        <v>0.2042293853199988</v>
+        <v>0.1104663920799984</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1453946945954663</v>
+        <v>0.1477659968477393</v>
       </c>
       <c r="T59">
-        <v>2.300108420218621</v>
+        <v>2.354872906414302</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.005731090614298697</v>
+        <v>0.005632278707155615</v>
       </c>
       <c r="W59">
-        <v>0.2344486088331484</v>
+        <v>0.2344719086808527</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.02221352951278566</v>
+        <v>0.02183053762463416</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1980554257109451</v>
+        <v>0.1999554257109451</v>
       </c>
       <c r="C60">
-        <v>-5.145818298885484</v>
+        <v>-5.893510423376483</v>
       </c>
       <c r="D60">
-        <v>23.40638170111452</v>
+        <v>23.19458957662352</v>
       </c>
       <c r="E60">
-        <v>21.1922</v>
+        <v>21.7281</v>
       </c>
       <c r="F60">
-        <v>31.0822</v>
+        <v>31.6181</v>
       </c>
       <c r="G60">
         <v>2.53</v>
@@ -6332,37 +6332,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M60">
-        <v>7.32918276</v>
+        <v>7.45554798</v>
       </c>
       <c r="N60">
-        <v>-7.16918276</v>
+        <v>-7.29554798</v>
       </c>
       <c r="O60">
-        <v>-1.84964915208</v>
+        <v>-1.88225137884</v>
       </c>
       <c r="P60">
-        <v>-5.31953360792</v>
+        <v>-5.41329660116</v>
       </c>
       <c r="Q60">
-        <v>0.1104663920799993</v>
+        <v>0.01670339883999983</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1477659968477393</v>
+        <v>0.1502529723806109</v>
       </c>
       <c r="T60">
-        <v>2.354872906414302</v>
+        <v>2.412308830960992</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.005632278707155617</v>
+        <v>0.005536816356186877</v>
       </c>
       <c r="W60">
-        <v>0.2344719086808527</v>
+        <v>0.2344944187032111</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.02183053762463416</v>
+        <v>0.02146052851235225</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1999554257109451</v>
+        <v>0.2018554257109451</v>
       </c>
       <c r="C61">
-        <v>-5.893510423376483</v>
+        <v>-6.637404125150496</v>
       </c>
       <c r="D61">
-        <v>23.19458957662352</v>
+        <v>22.98659587484951</v>
       </c>
       <c r="E61">
-        <v>21.7281</v>
+        <v>22.264</v>
       </c>
       <c r="F61">
-        <v>31.6181</v>
+        <v>32.154</v>
       </c>
       <c r="G61">
         <v>2.53</v>
@@ -6414,37 +6414,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M61">
-        <v>7.45554798</v>
+        <v>7.581913200000001</v>
       </c>
       <c r="N61">
-        <v>-7.29554798</v>
+        <v>-7.421913200000001</v>
       </c>
       <c r="O61">
-        <v>-1.88225137884</v>
+        <v>-1.9148536056</v>
       </c>
       <c r="P61">
-        <v>-5.41329660116</v>
+        <v>-5.5070595944</v>
       </c>
       <c r="Q61">
-        <v>0.01670339883999983</v>
+        <v>-0.07705959440000054</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1502529723806109</v>
+        <v>0.1528642966901262</v>
       </c>
       <c r="T61">
-        <v>2.412308830960992</v>
+        <v>2.472616551735017</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.005536816356186877</v>
+        <v>0.005444536083583763</v>
       </c>
       <c r="W61">
-        <v>0.2344944187032111</v>
+        <v>0.234516178391491</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.02146052851235225</v>
+        <v>0.02110285303714632</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2018554257109451</v>
+        <v>0.2037554257109451</v>
       </c>
       <c r="C62">
-        <v>-6.637404125150496</v>
+        <v>-7.377600681232256</v>
       </c>
       <c r="D62">
-        <v>22.98659587484951</v>
+        <v>22.78229931876774</v>
       </c>
       <c r="E62">
-        <v>22.264</v>
+        <v>22.7999</v>
       </c>
       <c r="F62">
-        <v>32.154</v>
+        <v>32.6899</v>
       </c>
       <c r="G62">
         <v>2.53</v>
@@ -6496,37 +6496,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M62">
-        <v>7.581913200000001</v>
+        <v>7.708278420000001</v>
       </c>
       <c r="N62">
-        <v>-7.421913200000001</v>
+        <v>-7.548278420000001</v>
       </c>
       <c r="O62">
-        <v>-1.9148536056</v>
+        <v>-1.94745583236</v>
       </c>
       <c r="P62">
-        <v>-5.5070595944</v>
+        <v>-5.600822587640001</v>
       </c>
       <c r="Q62">
-        <v>-0.07705959440000054</v>
+        <v>-0.1708225876400009</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1528642966901262</v>
+        <v>0.1556095350667961</v>
       </c>
       <c r="T62">
-        <v>2.472616551735017</v>
+        <v>2.536016976138479</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.005444536083583763</v>
+        <v>0.005355281393688947</v>
       </c>
       <c r="W62">
-        <v>0.234516178391491</v>
+        <v>0.2345372246473682</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.02110285303714632</v>
+        <v>0.02075690462670132</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2037554257109451</v>
+        <v>0.2056554257109451</v>
       </c>
       <c r="C63">
-        <v>-7.377600681232256</v>
+        <v>-8.114197799909764</v>
       </c>
       <c r="D63">
-        <v>22.78229931876774</v>
+        <v>22.58160220009023</v>
       </c>
       <c r="E63">
-        <v>22.7999</v>
+        <v>23.3358</v>
       </c>
       <c r="F63">
-        <v>32.6899</v>
+        <v>33.2258</v>
       </c>
       <c r="G63">
         <v>2.53</v>
@@ -6578,37 +6578,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M63">
-        <v>7.708278420000001</v>
+        <v>7.83464364</v>
       </c>
       <c r="N63">
-        <v>-7.548278420000001</v>
+        <v>-7.67464364</v>
       </c>
       <c r="O63">
-        <v>-1.94745583236</v>
+        <v>-1.98005805912</v>
       </c>
       <c r="P63">
-        <v>-5.600822587640001</v>
+        <v>-5.69458558088</v>
       </c>
       <c r="Q63">
-        <v>-0.1708225876400009</v>
+        <v>-0.2645855808800004</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1556095350667961</v>
+        <v>0.1584992596738171</v>
       </c>
       <c r="T63">
-        <v>2.536016976138479</v>
+        <v>2.602754264984228</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.005355281393688947</v>
+        <v>0.005268905887339126</v>
       </c>
       <c r="W63">
-        <v>0.2345372246473682</v>
+        <v>0.2345575919917655</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.02075690462670132</v>
+        <v>0.02042211584239972</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2056554257109451</v>
+        <v>0.2075554257109451</v>
       </c>
       <c r="C64">
-        <v>-8.114197799909764</v>
+        <v>-8.847289776552813</v>
       </c>
       <c r="D64">
-        <v>22.58160220009023</v>
+        <v>22.38441022344719</v>
       </c>
       <c r="E64">
-        <v>23.3358</v>
+        <v>23.8717</v>
       </c>
       <c r="F64">
-        <v>33.2258</v>
+        <v>33.7617</v>
       </c>
       <c r="G64">
         <v>2.53</v>
@@ -6660,37 +6660,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M64">
-        <v>7.83464364</v>
+        <v>7.961008860000002</v>
       </c>
       <c r="N64">
-        <v>-7.67464364</v>
+        <v>-7.801008860000001</v>
       </c>
       <c r="O64">
-        <v>-1.98005805912</v>
+        <v>-2.01266028588</v>
       </c>
       <c r="P64">
-        <v>-5.69458558088</v>
+        <v>-5.78834857412</v>
       </c>
       <c r="Q64">
-        <v>-0.2645855808800004</v>
+        <v>-0.3583485741200008</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1584992596738171</v>
+        <v>0.1615451856109473</v>
       </c>
       <c r="T64">
-        <v>2.602754264984228</v>
+        <v>2.673098974848667</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.005268905887339126</v>
+        <v>0.005185272460555964</v>
       </c>
       <c r="W64">
-        <v>0.2345575919917655</v>
+        <v>0.2345773127538009</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.02042211584239972</v>
+        <v>0.02009795527347269</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2075554257109451</v>
+        <v>0.2094554257109451</v>
       </c>
       <c r="C65">
-        <v>-8.847289776552813</v>
+        <v>-9.576967641338076</v>
       </c>
       <c r="D65">
-        <v>22.38441022344719</v>
+        <v>22.19063235866193</v>
       </c>
       <c r="E65">
-        <v>23.8717</v>
+        <v>24.4076</v>
       </c>
       <c r="F65">
-        <v>33.7617</v>
+        <v>34.2976</v>
       </c>
       <c r="G65">
         <v>2.53</v>
@@ -6742,37 +6742,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M65">
-        <v>7.961008860000002</v>
+        <v>8.087374080000002</v>
       </c>
       <c r="N65">
-        <v>-7.801008860000001</v>
+        <v>-7.927374080000002</v>
       </c>
       <c r="O65">
-        <v>-2.01266028588</v>
+        <v>-2.04526251264</v>
       </c>
       <c r="P65">
-        <v>-5.78834857412</v>
+        <v>-5.882111567360001</v>
       </c>
       <c r="Q65">
-        <v>-0.3583485741200008</v>
+        <v>-0.4521115673600011</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1615451856109473</v>
+        <v>0.1647603296556958</v>
       </c>
       <c r="T65">
-        <v>2.673098974848667</v>
+        <v>2.747351724150019</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.005185272460555964</v>
+        <v>0.005104252578359777</v>
       </c>
       <c r="W65">
-        <v>0.2345773127538009</v>
+        <v>0.2345964172420228</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.02009795527347269</v>
+        <v>0.01978392472232471</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2094554257109451</v>
+        <v>0.2113554257109451</v>
       </c>
       <c r="C66">
-        <v>-9.576967641338076</v>
+        <v>-10.30331929936716</v>
       </c>
       <c r="D66">
-        <v>22.19063235866193</v>
+        <v>22.00018070063284</v>
       </c>
       <c r="E66">
-        <v>24.4076</v>
+        <v>24.9435</v>
       </c>
       <c r="F66">
-        <v>34.2976</v>
+        <v>34.8335</v>
       </c>
       <c r="G66">
         <v>2.53</v>
@@ -6824,37 +6824,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M66">
-        <v>8.087374080000002</v>
+        <v>8.2137393</v>
       </c>
       <c r="N66">
-        <v>-7.927374080000002</v>
+        <v>-8.0537393</v>
       </c>
       <c r="O66">
-        <v>-2.04526251264</v>
+        <v>-2.0778647394</v>
       </c>
       <c r="P66">
-        <v>-5.882111567360001</v>
+        <v>-5.975874560599999</v>
       </c>
       <c r="Q66">
-        <v>-0.4521115673600011</v>
+        <v>-0.5458745605999997</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1647603296556958</v>
+        <v>0.1681591962172871</v>
       </c>
       <c r="T66">
-        <v>2.747351724150019</v>
+        <v>2.825847487697162</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.005104252578359777</v>
+        <v>0.005025725615615781</v>
       </c>
       <c r="W66">
-        <v>0.2345964172420228</v>
+        <v>0.2346149338998378</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.01978392472232471</v>
+        <v>0.0194795566496736</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2113554257109451</v>
+        <v>0.2132554257109451</v>
       </c>
       <c r="C67">
-        <v>-10.30331929936716</v>
+        <v>-11.02642966363058</v>
       </c>
       <c r="D67">
-        <v>22.00018070063284</v>
+        <v>21.81297033636942</v>
       </c>
       <c r="E67">
-        <v>24.9435</v>
+        <v>25.47940000000001</v>
       </c>
       <c r="F67">
-        <v>34.8335</v>
+        <v>35.36940000000001</v>
       </c>
       <c r="G67">
         <v>2.53</v>
@@ -6906,37 +6906,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M67">
-        <v>8.2137393</v>
+        <v>8.340104520000002</v>
       </c>
       <c r="N67">
-        <v>-8.0537393</v>
+        <v>-8.180104520000002</v>
       </c>
       <c r="O67">
-        <v>-2.0778647394</v>
+        <v>-2.110466966160001</v>
       </c>
       <c r="P67">
-        <v>-5.975874560599999</v>
+        <v>-6.069637553840002</v>
       </c>
       <c r="Q67">
-        <v>-0.5458745605999997</v>
+        <v>-0.6396375538400019</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1681591962172871</v>
+        <v>0.1717579961060309</v>
       </c>
       <c r="T67">
-        <v>2.825847487697162</v>
+        <v>2.90896064910002</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.005025725615615781</v>
+        <v>0.00494957825780342</v>
       </c>
       <c r="W67">
-        <v>0.2346149338998378</v>
+        <v>0.23463288944681</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.0194795566496736</v>
+        <v>0.01918441185195119</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2132554257109451</v>
+        <v>0.2151554257109451</v>
       </c>
       <c r="C68">
-        <v>-11.02642966363058</v>
+        <v>-11.74638078124033</v>
       </c>
       <c r="D68">
-        <v>21.81297033636942</v>
+        <v>21.62891921875967</v>
       </c>
       <c r="E68">
-        <v>25.47940000000001</v>
+        <v>26.0153</v>
       </c>
       <c r="F68">
-        <v>35.36940000000001</v>
+        <v>35.9053</v>
       </c>
       <c r="G68">
         <v>2.53</v>
@@ -6988,37 +6988,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M68">
-        <v>8.340104520000002</v>
+        <v>8.466469740000001</v>
       </c>
       <c r="N68">
-        <v>-8.180104520000002</v>
+        <v>-8.306469740000001</v>
       </c>
       <c r="O68">
-        <v>-2.110466966160001</v>
+        <v>-2.14306919292</v>
       </c>
       <c r="P68">
-        <v>-6.069637553840002</v>
+        <v>-6.16340054708</v>
       </c>
       <c r="Q68">
-        <v>-0.6396375538400019</v>
+        <v>-0.7334005470800005</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1717579961060309</v>
+        <v>0.1755749050789409</v>
       </c>
       <c r="T68">
-        <v>2.90896064910002</v>
+        <v>2.997110971800022</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.00494957825780342</v>
+        <v>0.004875703955448145</v>
       </c>
       <c r="W68">
-        <v>0.23463288944681</v>
+        <v>0.2346503090073054</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.01918441185195119</v>
+        <v>0.01889807734669824</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2151554257109451</v>
+        <v>0.2170554257109451</v>
       </c>
       <c r="C69">
-        <v>-11.74638078124033</v>
+        <v>-12.46325195332525</v>
       </c>
       <c r="D69">
-        <v>21.62891921875967</v>
+        <v>21.44794804667475</v>
       </c>
       <c r="E69">
-        <v>26.0153</v>
+        <v>26.5512</v>
       </c>
       <c r="F69">
-        <v>35.9053</v>
+        <v>36.4412</v>
       </c>
       <c r="G69">
         <v>2.53</v>
@@ -7070,37 +7070,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M69">
-        <v>8.466469740000001</v>
+        <v>8.592834960000001</v>
       </c>
       <c r="N69">
-        <v>-8.306469740000001</v>
+        <v>-8.432834960000001</v>
       </c>
       <c r="O69">
-        <v>-2.14306919292</v>
+        <v>-2.17567141968</v>
       </c>
       <c r="P69">
-        <v>-6.16340054708</v>
+        <v>-6.257163540320001</v>
       </c>
       <c r="Q69">
-        <v>-0.7334005470800005</v>
+        <v>-0.8271635403200008</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1755749050789409</v>
+        <v>0.1796303708626578</v>
       </c>
       <c r="T69">
-        <v>2.997110971800022</v>
+        <v>3.090770689668772</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.004875703955448145</v>
+        <v>0.004804002426691555</v>
       </c>
       <c r="W69">
-        <v>0.2346503090073054</v>
+        <v>0.2346672162277861</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.01889807734669824</v>
+        <v>0.01862016444454095</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2170554257109451</v>
+        <v>0.2189554257109451</v>
       </c>
       <c r="C70">
-        <v>-12.46325195332525</v>
+        <v>-13.17711984895726</v>
       </c>
       <c r="D70">
-        <v>21.44794804667475</v>
+        <v>21.26998015104274</v>
       </c>
       <c r="E70">
-        <v>26.5512</v>
+        <v>27.08710000000001</v>
       </c>
       <c r="F70">
-        <v>36.4412</v>
+        <v>36.97710000000001</v>
       </c>
       <c r="G70">
         <v>2.53</v>
@@ -7152,37 +7152,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M70">
-        <v>8.592834960000001</v>
+        <v>8.719200180000001</v>
       </c>
       <c r="N70">
-        <v>-8.432834960000001</v>
+        <v>-8.559200180000001</v>
       </c>
       <c r="O70">
-        <v>-2.17567141968</v>
+        <v>-2.20827364644</v>
       </c>
       <c r="P70">
-        <v>-6.257163540320001</v>
+        <v>-6.350926533560001</v>
       </c>
       <c r="Q70">
-        <v>-0.8271635403200008</v>
+        <v>-0.9209265335600012</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1796303708626578</v>
+        <v>0.1839474796001629</v>
       </c>
       <c r="T70">
-        <v>3.090770689668772</v>
+        <v>3.190472969980668</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.004804002426691555</v>
+        <v>0.004734379203116315</v>
       </c>
       <c r="W70">
-        <v>0.2346672162277861</v>
+        <v>0.2346836333839052</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.01862016444454095</v>
+        <v>0.0183503069888229</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2189554257109451</v>
+        <v>0.2208554257109451</v>
       </c>
       <c r="C71">
-        <v>-13.17711984895726</v>
+        <v>-13.88805861345233</v>
       </c>
       <c r="D71">
-        <v>21.26998015104274</v>
+        <v>21.09494138654768</v>
       </c>
       <c r="E71">
-        <v>27.08710000000001</v>
+        <v>27.623</v>
       </c>
       <c r="F71">
-        <v>36.97710000000001</v>
+        <v>37.51300000000001</v>
       </c>
       <c r="G71">
         <v>2.53</v>
@@ -7234,37 +7234,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M71">
-        <v>8.719200180000001</v>
+        <v>8.845565400000002</v>
       </c>
       <c r="N71">
-        <v>-8.559200180000001</v>
+        <v>-8.685565400000002</v>
       </c>
       <c r="O71">
-        <v>-2.20827364644</v>
+        <v>-2.2408758732</v>
       </c>
       <c r="P71">
-        <v>-6.350926533560001</v>
+        <v>-6.444689526800001</v>
       </c>
       <c r="Q71">
-        <v>-0.9209265335600012</v>
+        <v>-1.014689526800002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1839474796001629</v>
+        <v>0.188552395586835</v>
       </c>
       <c r="T71">
-        <v>3.190472969980668</v>
+        <v>3.296822068980023</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.004734379203116315</v>
+        <v>0.004666745214500368</v>
       </c>
       <c r="W71">
-        <v>0.2346836333839052</v>
+        <v>0.2346995814784208</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.0183503069888229</v>
+        <v>0.01808815974612543</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2208554257109451</v>
+        <v>0.2227554257109451</v>
       </c>
       <c r="C72">
-        <v>-13.88805861345233</v>
+        <v>-14.59613997136765</v>
       </c>
       <c r="D72">
-        <v>21.09494138654768</v>
+        <v>20.92276002863235</v>
       </c>
       <c r="E72">
-        <v>27.623</v>
+        <v>28.1589</v>
       </c>
       <c r="F72">
-        <v>37.51300000000001</v>
+        <v>38.0489</v>
       </c>
       <c r="G72">
         <v>2.53</v>
@@ -7316,37 +7316,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M72">
-        <v>8.845565400000002</v>
+        <v>8.971930620000002</v>
       </c>
       <c r="N72">
-        <v>-8.685565400000002</v>
+        <v>-8.811930620000002</v>
       </c>
       <c r="O72">
-        <v>-2.2408758732</v>
+        <v>-2.273478099960001</v>
       </c>
       <c r="P72">
-        <v>-6.444689526800001</v>
+        <v>-6.538452520040002</v>
       </c>
       <c r="Q72">
-        <v>-1.014689526800002</v>
+        <v>-1.108452520040002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.188552395586835</v>
+        <v>0.1934748919863811</v>
       </c>
       <c r="T72">
-        <v>3.296822068980023</v>
+        <v>3.410505588600024</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.004666745214500368</v>
+        <v>0.004601016408662334</v>
       </c>
       <c r="W72">
-        <v>0.2346995814784208</v>
+        <v>0.2347150803308374</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.01808815974612543</v>
+        <v>0.01783339693279973</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2227554257109451</v>
+        <v>0.2246554257109451</v>
       </c>
       <c r="C73">
-        <v>-14.59613997136764</v>
+        <v>-15.30143332449551</v>
       </c>
       <c r="D73">
-        <v>20.92276002863236</v>
+        <v>20.75336667550449</v>
       </c>
       <c r="E73">
-        <v>28.1589</v>
+        <v>28.6948</v>
       </c>
       <c r="F73">
-        <v>38.0489</v>
+        <v>38.5848</v>
       </c>
       <c r="G73">
         <v>2.53</v>
@@ -7398,37 +7398,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M73">
-        <v>8.971930620000002</v>
+        <v>9.09829584</v>
       </c>
       <c r="N73">
-        <v>-8.811930620000002</v>
+        <v>-8.93829584</v>
       </c>
       <c r="O73">
-        <v>-2.273478099960001</v>
+        <v>-2.30608032672</v>
       </c>
       <c r="P73">
-        <v>-6.538452520040002</v>
+        <v>-6.63221551328</v>
       </c>
       <c r="Q73">
-        <v>-1.108452520040002</v>
+        <v>-1.202215513280001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.193474891986381</v>
+        <v>0.1987489952716089</v>
       </c>
       <c r="T73">
-        <v>3.410505588600023</v>
+        <v>3.532309359621453</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.004601016408662334</v>
+        <v>0.004537113402986469</v>
       </c>
       <c r="W73">
-        <v>0.2347150803308374</v>
+        <v>0.2347301486595758</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.01783339693279973</v>
+        <v>0.01758571086428862</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2246554257109451</v>
+        <v>0.2265554257109451</v>
       </c>
       <c r="C74">
-        <v>-15.30143332449551</v>
+        <v>-16.00400584513514</v>
       </c>
       <c r="D74">
-        <v>20.75336667550449</v>
+        <v>20.58669415486486</v>
       </c>
       <c r="E74">
-        <v>28.6948</v>
+        <v>29.2307</v>
       </c>
       <c r="F74">
-        <v>38.5848</v>
+        <v>39.1207</v>
       </c>
       <c r="G74">
         <v>2.53</v>
@@ -7480,37 +7480,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M74">
-        <v>9.09829584</v>
+        <v>9.224661060000001</v>
       </c>
       <c r="N74">
-        <v>-8.93829584</v>
+        <v>-9.064661060000001</v>
       </c>
       <c r="O74">
-        <v>-2.30608032672</v>
+        <v>-2.33868255348</v>
       </c>
       <c r="P74">
-        <v>-6.63221551328</v>
+        <v>-6.725978506520001</v>
       </c>
       <c r="Q74">
-        <v>-1.202215513280001</v>
+        <v>-1.295978506520001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1987489952716089</v>
+        <v>0.2044137728742611</v>
       </c>
       <c r="T74">
-        <v>3.532309359621453</v>
+        <v>3.663135632200025</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.004537113402986469</v>
+        <v>0.004474961164589395</v>
       </c>
       <c r="W74">
-        <v>0.2347301486595758</v>
+        <v>0.2347448041573899</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.01758571086428862</v>
+        <v>0.01734481071546279</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2265554257109451</v>
+        <v>0.2284554257109451</v>
       </c>
       <c r="C75">
-        <v>-16.00400584513514</v>
+        <v>-16.70392256490597</v>
       </c>
       <c r="D75">
-        <v>20.58669415486486</v>
+        <v>20.42267743509403</v>
       </c>
       <c r="E75">
-        <v>29.2307</v>
+        <v>29.7666</v>
       </c>
       <c r="F75">
-        <v>39.1207</v>
+        <v>39.6566</v>
       </c>
       <c r="G75">
         <v>2.53</v>
@@ -7562,37 +7562,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M75">
-        <v>9.224661060000001</v>
+        <v>9.351026280000001</v>
       </c>
       <c r="N75">
-        <v>-9.064661060000001</v>
+        <v>-9.191026280000001</v>
       </c>
       <c r="O75">
-        <v>-2.33868255348</v>
+        <v>-2.37128478024</v>
       </c>
       <c r="P75">
-        <v>-6.725978506520001</v>
+        <v>-6.819741499760001</v>
       </c>
       <c r="Q75">
-        <v>-1.295978506520001</v>
+        <v>-1.389741499760001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2044137728742611</v>
+        <v>0.2105143026001942</v>
       </c>
       <c r="T75">
-        <v>3.663135632200025</v>
+        <v>3.804025464207718</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.004474961164589395</v>
+        <v>0.004414488716419267</v>
       </c>
       <c r="W75">
-        <v>0.2347448041573899</v>
+        <v>0.2347590635606684</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.01734481071546279</v>
+        <v>0.01711042138147001</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2284554257109451</v>
+        <v>0.2303554257109451</v>
       </c>
       <c r="C76">
-        <v>-16.70392256490597</v>
+        <v>-17.40124645934883</v>
       </c>
       <c r="D76">
-        <v>20.42267743509403</v>
+        <v>20.26125354065117</v>
       </c>
       <c r="E76">
-        <v>29.7666</v>
+        <v>30.3025</v>
       </c>
       <c r="F76">
-        <v>39.6566</v>
+        <v>40.1925</v>
       </c>
       <c r="G76">
         <v>2.53</v>
@@ -7644,37 +7644,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M76">
-        <v>9.351026280000001</v>
+        <v>9.477391500000001</v>
       </c>
       <c r="N76">
-        <v>-9.191026280000001</v>
+        <v>-9.317391500000001</v>
       </c>
       <c r="O76">
-        <v>-2.37128478024</v>
+        <v>-2.403887007</v>
       </c>
       <c r="P76">
-        <v>-6.819741499760001</v>
+        <v>-6.913504493000001</v>
       </c>
       <c r="Q76">
-        <v>-1.389741499760001</v>
+        <v>-1.483504493000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2105143026001942</v>
+        <v>0.217102874704202</v>
       </c>
       <c r="T76">
-        <v>3.804025464207718</v>
+        <v>3.956186482776027</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.004414488716419267</v>
+        <v>0.00435562886686701</v>
       </c>
       <c r="W76">
-        <v>0.2347590635606684</v>
+        <v>0.2347729427131928</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.01711042138147001</v>
+        <v>0.01688228242971712</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2303554257109451</v>
+        <v>0.232255425710945</v>
       </c>
       <c r="C77">
-        <v>-17.40124645934883</v>
+        <v>-18.09603852854658</v>
       </c>
       <c r="D77">
-        <v>20.26125354065117</v>
+        <v>20.10236147145342</v>
       </c>
       <c r="E77">
-        <v>30.3025</v>
+        <v>30.8384</v>
       </c>
       <c r="F77">
-        <v>40.1925</v>
+        <v>40.7284</v>
       </c>
       <c r="G77">
         <v>2.53</v>
@@ -7726,37 +7726,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M77">
-        <v>9.477391500000001</v>
+        <v>9.60375672</v>
       </c>
       <c r="N77">
-        <v>-9.317391500000001</v>
+        <v>-9.44375672</v>
       </c>
       <c r="O77">
-        <v>-2.403887007</v>
+        <v>-2.43648923376</v>
       </c>
       <c r="P77">
-        <v>-6.913504493000001</v>
+        <v>-7.00726748624</v>
       </c>
       <c r="Q77">
-        <v>-1.483504493000002</v>
+        <v>-1.57726748624</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.217102874704202</v>
+        <v>0.2242404944835437</v>
       </c>
       <c r="T77">
-        <v>3.956186482776027</v>
+        <v>4.121027586225028</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.00435562886686701</v>
+        <v>0.004298317960724024</v>
       </c>
       <c r="W77">
-        <v>0.2347729427131928</v>
+        <v>0.2347864566248613</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.01688228242971712</v>
+        <v>0.01666014713458919</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.232255425710945</v>
+        <v>0.2341554257109451</v>
       </c>
       <c r="C78">
-        <v>-18.09603852854658</v>
+        <v>-18.78835787398063</v>
       </c>
       <c r="D78">
-        <v>20.10236147145342</v>
+        <v>19.94594212601938</v>
       </c>
       <c r="E78">
-        <v>30.8384</v>
+        <v>31.37430000000001</v>
       </c>
       <c r="F78">
-        <v>40.7284</v>
+        <v>41.26430000000001</v>
       </c>
       <c r="G78">
         <v>2.53</v>
@@ -7808,37 +7808,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M78">
-        <v>9.60375672</v>
+        <v>9.730121940000002</v>
       </c>
       <c r="N78">
-        <v>-9.44375672</v>
+        <v>-9.570121940000002</v>
       </c>
       <c r="O78">
-        <v>-2.43648923376</v>
+        <v>-2.469091460520001</v>
       </c>
       <c r="P78">
-        <v>-7.00726748624</v>
+        <v>-7.101030479480001</v>
       </c>
       <c r="Q78">
-        <v>-1.57726748624</v>
+        <v>-1.671030479480001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2242404944835437</v>
+        <v>0.2319987768523935</v>
       </c>
       <c r="T78">
-        <v>4.121027586225028</v>
+        <v>4.300202698669596</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.004298317960724024</v>
+        <v>0.004242495649545789</v>
       </c>
       <c r="W78">
-        <v>0.2347864566248613</v>
+        <v>0.2347996195258371</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.01666014713458919</v>
+        <v>0.0164437815873868</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2341554257109451</v>
+        <v>0.2360554257109451</v>
       </c>
       <c r="C79">
-        <v>-18.78835787398063</v>
+        <v>-19.47826177182706</v>
       </c>
       <c r="D79">
-        <v>19.94594212601938</v>
+        <v>19.79193822817294</v>
       </c>
       <c r="E79">
-        <v>31.37430000000001</v>
+        <v>31.9102</v>
       </c>
       <c r="F79">
-        <v>41.26430000000001</v>
+        <v>41.8002</v>
       </c>
       <c r="G79">
         <v>2.53</v>
@@ -7890,37 +7890,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M79">
-        <v>9.730121940000002</v>
+        <v>9.856487160000002</v>
       </c>
       <c r="N79">
-        <v>-9.570121940000002</v>
+        <v>-9.696487160000002</v>
       </c>
       <c r="O79">
-        <v>-2.469091460520001</v>
+        <v>-2.50169368728</v>
       </c>
       <c r="P79">
-        <v>-7.101030479480001</v>
+        <v>-7.194793472720002</v>
       </c>
       <c r="Q79">
-        <v>-1.671030479480001</v>
+        <v>-1.764793472720002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2319987768523935</v>
+        <v>0.2404623576184114</v>
       </c>
       <c r="T79">
-        <v>4.300202698669596</v>
+        <v>4.495666457700032</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.004242495649545789</v>
+        <v>0.004188104679679817</v>
       </c>
       <c r="W79">
-        <v>0.2347996195258371</v>
+        <v>0.2348124449165315</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.0164437815873868</v>
+        <v>0.01623296387472795</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2360554257109451</v>
+        <v>0.2379554257109451</v>
       </c>
       <c r="C80">
-        <v>-19.47826177182706</v>
+        <v>-20.16580574288327</v>
       </c>
       <c r="D80">
-        <v>19.79193822817294</v>
+        <v>19.64029425711673</v>
       </c>
       <c r="E80">
-        <v>31.9102</v>
+        <v>32.4461</v>
       </c>
       <c r="F80">
-        <v>41.8002</v>
+        <v>42.3361</v>
       </c>
       <c r="G80">
         <v>2.53</v>
@@ -7972,37 +7972,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M80">
-        <v>9.856487160000002</v>
+        <v>9.982852380000001</v>
       </c>
       <c r="N80">
-        <v>-9.696487160000002</v>
+        <v>-9.82285238</v>
       </c>
       <c r="O80">
-        <v>-2.50169368728</v>
+        <v>-2.53429591404</v>
       </c>
       <c r="P80">
-        <v>-7.194793472720002</v>
+        <v>-7.28855646596</v>
       </c>
       <c r="Q80">
-        <v>-1.764793472720002</v>
+        <v>-1.85855646596</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2404623576184114</v>
+        <v>0.2497319936954786</v>
       </c>
       <c r="T80">
-        <v>4.495666457700032</v>
+        <v>4.709745812828605</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.004188104679679817</v>
+        <v>0.004135090696392732</v>
       </c>
       <c r="W80">
-        <v>0.2348124449165315</v>
+        <v>0.2348249456137906</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.01623296387472795</v>
+        <v>0.01602748331935167</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2379554257109451</v>
+        <v>0.2398554257109451</v>
       </c>
       <c r="C81">
-        <v>-20.16580574288327</v>
+        <v>-20.85104361930432</v>
       </c>
       <c r="D81">
-        <v>19.64029425711673</v>
+        <v>19.49095638069569</v>
       </c>
       <c r="E81">
-        <v>32.4461</v>
+        <v>32.98200000000001</v>
       </c>
       <c r="F81">
-        <v>42.3361</v>
+        <v>42.87200000000001</v>
       </c>
       <c r="G81">
         <v>2.53</v>
@@ -8054,37 +8054,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M81">
-        <v>9.982852380000001</v>
+        <v>10.1092176</v>
       </c>
       <c r="N81">
-        <v>-9.82285238</v>
+        <v>-9.949217600000003</v>
       </c>
       <c r="O81">
-        <v>-2.53429591404</v>
+        <v>-2.566898140800001</v>
       </c>
       <c r="P81">
-        <v>-7.28855646596</v>
+        <v>-7.382319459200001</v>
       </c>
       <c r="Q81">
-        <v>-1.85855646596</v>
+        <v>-1.952319459200002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2497319936954786</v>
+        <v>0.2599285933802525</v>
       </c>
       <c r="T81">
-        <v>4.709745812828605</v>
+        <v>4.945233103470034</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.004135090696392732</v>
+        <v>0.004083402062687822</v>
       </c>
       <c r="W81">
-        <v>0.2348249456137906</v>
+        <v>0.2348371337936182</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.01602748331935167</v>
+        <v>0.01582713977785977</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2398554257109451</v>
+        <v>0.241755425710945</v>
       </c>
       <c r="C82">
-        <v>-20.85104361930432</v>
+        <v>-21.53402760831773</v>
       </c>
       <c r="D82">
-        <v>19.49095638069569</v>
+        <v>19.34387239168228</v>
       </c>
       <c r="E82">
-        <v>32.98200000000001</v>
+        <v>33.5179</v>
       </c>
       <c r="F82">
-        <v>42.87200000000001</v>
+        <v>43.40790000000001</v>
       </c>
       <c r="G82">
         <v>2.53</v>
@@ -8136,37 +8136,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M82">
-        <v>10.1092176</v>
+        <v>10.23558282</v>
       </c>
       <c r="N82">
-        <v>-9.949217600000003</v>
+        <v>-10.07558282</v>
       </c>
       <c r="O82">
-        <v>-2.566898140800001</v>
+        <v>-2.59950036756</v>
       </c>
       <c r="P82">
-        <v>-7.382319459200001</v>
+        <v>-7.476082452440001</v>
       </c>
       <c r="Q82">
-        <v>-1.952319459200002</v>
+        <v>-2.046082452440001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2599285933802525</v>
+        <v>0.2711985193476342</v>
       </c>
       <c r="T82">
-        <v>4.945233103470034</v>
+        <v>5.205508529968458</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.004083402062687822</v>
+        <v>0.004032989691543528</v>
       </c>
       <c r="W82">
-        <v>0.2348371337936182</v>
+        <v>0.234849021030734</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.01582713977785977</v>
+        <v>0.01563174299047876</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.241755425710945</v>
+        <v>0.2436554257109451</v>
       </c>
       <c r="C83">
-        <v>-21.53402760831773</v>
+        <v>-22.2148083530749</v>
       </c>
       <c r="D83">
-        <v>19.34387239168228</v>
+        <v>19.1989916469251</v>
       </c>
       <c r="E83">
-        <v>33.5179</v>
+        <v>34.0538</v>
       </c>
       <c r="F83">
-        <v>43.40790000000001</v>
+        <v>43.9438</v>
       </c>
       <c r="G83">
         <v>2.53</v>
@@ -8218,37 +8218,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M83">
-        <v>10.23558282</v>
+        <v>10.36194804</v>
       </c>
       <c r="N83">
-        <v>-10.07558282</v>
+        <v>-10.20194804</v>
       </c>
       <c r="O83">
-        <v>-2.59950036756</v>
+        <v>-2.63210259432</v>
       </c>
       <c r="P83">
-        <v>-7.476082452440001</v>
+        <v>-7.56984544568</v>
       </c>
       <c r="Q83">
-        <v>-2.046082452440001</v>
+        <v>-2.139845445680001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2711985193476342</v>
+        <v>0.2837206593113917</v>
       </c>
       <c r="T83">
-        <v>5.205508529968458</v>
+        <v>5.49470344830004</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.004032989691543528</v>
+        <v>0.003983806890427143</v>
       </c>
       <c r="W83">
-        <v>0.234849021030734</v>
+        <v>0.2348606183352373</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.01563174299047876</v>
+        <v>0.01544111197839981</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2436554257109451</v>
+        <v>0.2455554257109451</v>
       </c>
       <c r="C84">
-        <v>-22.2148083530749</v>
+        <v>-22.89343499078844</v>
       </c>
       <c r="D84">
-        <v>19.1989916469251</v>
+        <v>19.05626500921157</v>
       </c>
       <c r="E84">
-        <v>34.0538</v>
+        <v>34.58970000000001</v>
       </c>
       <c r="F84">
-        <v>43.9438</v>
+        <v>44.47970000000001</v>
       </c>
       <c r="G84">
         <v>2.53</v>
@@ -8300,37 +8300,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M84">
-        <v>10.36194804</v>
+        <v>10.48831326</v>
       </c>
       <c r="N84">
-        <v>-10.20194804</v>
+        <v>-10.32831326</v>
       </c>
       <c r="O84">
-        <v>-2.63210259432</v>
+        <v>-2.66470482108</v>
       </c>
       <c r="P84">
-        <v>-7.56984544568</v>
+        <v>-7.663608438920001</v>
       </c>
       <c r="Q84">
-        <v>-2.139845445680001</v>
+        <v>-2.233608438920001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2837206593113917</v>
+        <v>0.2977159922120619</v>
       </c>
       <c r="T84">
-        <v>5.49470344830004</v>
+        <v>5.817921298200043</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.003983806890427143</v>
+        <v>0.003935809217048503</v>
       </c>
       <c r="W84">
-        <v>0.2348606183352373</v>
+        <v>0.23487193618662</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.01544111197839981</v>
+        <v>0.01525507448468411</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2455554257109451</v>
+        <v>0.2474554257109451</v>
       </c>
       <c r="C85">
-        <v>-22.89343499078844</v>
+        <v>-23.56995520829533</v>
       </c>
       <c r="D85">
-        <v>19.05626500921157</v>
+        <v>18.91564479170467</v>
       </c>
       <c r="E85">
-        <v>34.58970000000001</v>
+        <v>35.12560000000001</v>
       </c>
       <c r="F85">
-        <v>44.47970000000001</v>
+        <v>45.01560000000001</v>
       </c>
       <c r="G85">
         <v>2.53</v>
@@ -8382,37 +8382,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M85">
-        <v>10.48831326</v>
+        <v>10.61467848</v>
       </c>
       <c r="N85">
-        <v>-10.32831326</v>
+        <v>-10.45467848</v>
       </c>
       <c r="O85">
-        <v>-2.66470482108</v>
+        <v>-2.697307047840001</v>
       </c>
       <c r="P85">
-        <v>-7.663608438920001</v>
+        <v>-7.757371432160001</v>
       </c>
       <c r="Q85">
-        <v>-2.233608438920001</v>
+        <v>-2.327371432160001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2977159922120619</v>
+        <v>0.3134607417253157</v>
       </c>
       <c r="T85">
-        <v>5.817921298200043</v>
+        <v>6.181541379337546</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.003935809217048503</v>
+        <v>0.003888954345416973</v>
       </c>
       <c r="W85">
-        <v>0.23487193618662</v>
+        <v>0.2348829845653507</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.01525507448468411</v>
+        <v>0.01507346645510454</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2474554257109451</v>
+        <v>0.2493554257109451</v>
       </c>
       <c r="C86">
-        <v>-23.56995520829532</v>
+        <v>-24.24441529517809</v>
       </c>
       <c r="D86">
-        <v>18.91564479170468</v>
+        <v>18.77708470482191</v>
       </c>
       <c r="E86">
-        <v>35.1256</v>
+        <v>35.6615</v>
       </c>
       <c r="F86">
-        <v>45.0156</v>
+        <v>45.5515</v>
       </c>
       <c r="G86">
         <v>2.53</v>
@@ -8464,37 +8464,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M86">
-        <v>10.61467848</v>
+        <v>10.7410437</v>
       </c>
       <c r="N86">
-        <v>-10.45467848</v>
+        <v>-10.5810437</v>
       </c>
       <c r="O86">
-        <v>-2.69730704784</v>
+        <v>-2.729909274600001</v>
       </c>
       <c r="P86">
-        <v>-7.757371432159999</v>
+        <v>-7.851134425400002</v>
       </c>
       <c r="Q86">
-        <v>-2.32737143216</v>
+        <v>-2.421134425400002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3134607417253156</v>
+        <v>0.3313047911736699</v>
       </c>
       <c r="T86">
-        <v>6.181541379337542</v>
+        <v>6.593644137960045</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.003888954345416974</v>
+        <v>0.003843201941353244</v>
       </c>
       <c r="W86">
-        <v>0.2348829845653507</v>
+        <v>0.2348937729822289</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.01507346645510454</v>
+        <v>0.01489613155563274</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2493554257109451</v>
+        <v>0.2512554257109451</v>
       </c>
       <c r="C87">
-        <v>-24.24441529517809</v>
+        <v>-24.9168601945682</v>
       </c>
       <c r="D87">
-        <v>18.77708470482191</v>
+        <v>18.6405398054318</v>
       </c>
       <c r="E87">
-        <v>35.6615</v>
+        <v>36.1974</v>
       </c>
       <c r="F87">
-        <v>45.5515</v>
+        <v>46.0874</v>
       </c>
       <c r="G87">
         <v>2.53</v>
@@ -8546,37 +8546,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M87">
-        <v>10.7410437</v>
+        <v>10.86740892</v>
       </c>
       <c r="N87">
-        <v>-10.5810437</v>
+        <v>-10.70740892</v>
       </c>
       <c r="O87">
-        <v>-2.729909274600001</v>
+        <v>-2.76251150136</v>
       </c>
       <c r="P87">
-        <v>-7.851134425400002</v>
+        <v>-7.94489741864</v>
       </c>
       <c r="Q87">
-        <v>-2.421134425400002</v>
+        <v>-2.51489741864</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3313047911736699</v>
+        <v>0.3516979905432178</v>
       </c>
       <c r="T87">
-        <v>6.593644137960045</v>
+        <v>7.064618719242906</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.003843201941353244</v>
+        <v>0.003798513546686346</v>
       </c>
       <c r="W87">
-        <v>0.2348937729822289</v>
+        <v>0.2349043105056914</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.01489613155563274</v>
+        <v>0.01472292072359049</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2512554257109451</v>
+        <v>0.2531554257109451</v>
       </c>
       <c r="C88">
-        <v>-24.9168601945682</v>
+        <v>-25.58733355174884</v>
       </c>
       <c r="D88">
-        <v>18.6405398054318</v>
+        <v>18.50596644825116</v>
       </c>
       <c r="E88">
-        <v>36.1974</v>
+        <v>36.7333</v>
       </c>
       <c r="F88">
-        <v>46.0874</v>
+        <v>46.6233</v>
       </c>
       <c r="G88">
         <v>2.53</v>
@@ -8628,37 +8628,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M88">
-        <v>10.86740892</v>
+        <v>10.99377414</v>
       </c>
       <c r="N88">
-        <v>-10.70740892</v>
+        <v>-10.83377414</v>
       </c>
       <c r="O88">
-        <v>-2.76251150136</v>
+        <v>-2.79511372812</v>
       </c>
       <c r="P88">
-        <v>-7.94489741864</v>
+        <v>-8.03866041188</v>
       </c>
       <c r="Q88">
-        <v>-2.51489741864</v>
+        <v>-2.608660411880001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3516979905432178</v>
+        <v>0.3752286052003884</v>
       </c>
       <c r="T88">
-        <v>7.064618719242906</v>
+        <v>7.608050928415437</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.003798513546686346</v>
+        <v>0.003754852471437078</v>
       </c>
       <c r="W88">
-        <v>0.2349043105056914</v>
+        <v>0.2349146057872352</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.01472292072359049</v>
+        <v>0.01455369174975607</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2531554257109451</v>
+        <v>0.2550554257109451</v>
       </c>
       <c r="C89">
-        <v>-25.58733355174884</v>
+        <v>-26.25587776066753</v>
       </c>
       <c r="D89">
-        <v>18.50596644825116</v>
+        <v>18.37332223933248</v>
       </c>
       <c r="E89">
-        <v>36.7333</v>
+        <v>37.2692</v>
       </c>
       <c r="F89">
-        <v>46.6233</v>
+        <v>47.15920000000001</v>
       </c>
       <c r="G89">
         <v>2.53</v>
@@ -8710,37 +8710,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M89">
-        <v>10.99377414</v>
+        <v>11.12013936</v>
       </c>
       <c r="N89">
-        <v>-10.83377414</v>
+        <v>-10.96013936</v>
       </c>
       <c r="O89">
-        <v>-2.79511372812</v>
+        <v>-2.82771595488</v>
       </c>
       <c r="P89">
-        <v>-8.03866041188</v>
+        <v>-8.132423405120001</v>
       </c>
       <c r="Q89">
-        <v>-2.608660411880001</v>
+        <v>-2.702423405120001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3752286052003884</v>
+        <v>0.4026809889670874</v>
       </c>
       <c r="T89">
-        <v>7.608050928415437</v>
+        <v>8.242055172450057</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.003754852471437078</v>
+        <v>0.003712183693352565</v>
       </c>
       <c r="W89">
-        <v>0.2349146057872352</v>
+        <v>0.2349246670851075</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.01455369174975607</v>
+        <v>0.01438830888896347</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2550554257109451</v>
+        <v>0.256955425710945</v>
       </c>
       <c r="C90">
-        <v>-26.25587776066753</v>
+        <v>-26.92253400846257</v>
       </c>
       <c r="D90">
-        <v>18.37332223933248</v>
+        <v>18.24256599153744</v>
       </c>
       <c r="E90">
-        <v>37.2692</v>
+        <v>37.8051</v>
       </c>
       <c r="F90">
-        <v>47.15920000000001</v>
+        <v>47.6951</v>
       </c>
       <c r="G90">
         <v>2.53</v>
@@ -8792,37 +8792,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M90">
-        <v>11.12013936</v>
+        <v>11.24650458</v>
       </c>
       <c r="N90">
-        <v>-10.96013936</v>
+        <v>-11.08650458</v>
       </c>
       <c r="O90">
-        <v>-2.82771595488</v>
+        <v>-2.86031818164</v>
       </c>
       <c r="P90">
-        <v>-8.132423405120001</v>
+        <v>-8.226186398360001</v>
       </c>
       <c r="Q90">
-        <v>-2.702423405120001</v>
+        <v>-2.796186398360001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4026809889670874</v>
+        <v>0.4351247152368227</v>
       </c>
       <c r="T90">
-        <v>8.242055172450057</v>
+        <v>8.991332915400061</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.003712183693352565</v>
+        <v>0.003670473764213772</v>
       </c>
       <c r="W90">
-        <v>0.2349246670851075</v>
+        <v>0.2349345022863984</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.01438830888896347</v>
+        <v>0.0142266424969526</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.256955425710945</v>
+        <v>0.2588554257109451</v>
       </c>
       <c r="C91">
-        <v>-26.92253400846257</v>
+        <v>-27.58734231810178</v>
       </c>
       <c r="D91">
-        <v>18.24256599153744</v>
+        <v>18.11365768189822</v>
       </c>
       <c r="E91">
-        <v>37.8051</v>
+        <v>38.341</v>
       </c>
       <c r="F91">
-        <v>47.6951</v>
+        <v>48.231</v>
       </c>
       <c r="G91">
         <v>2.53</v>
@@ -8874,37 +8874,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M91">
-        <v>11.24650458</v>
+        <v>11.3728698</v>
       </c>
       <c r="N91">
-        <v>-11.08650458</v>
+        <v>-11.2128698</v>
       </c>
       <c r="O91">
-        <v>-2.86031818164</v>
+        <v>-2.8929204084</v>
       </c>
       <c r="P91">
-        <v>-8.226186398360001</v>
+        <v>-8.3199493916</v>
       </c>
       <c r="Q91">
-        <v>-2.796186398360001</v>
+        <v>-2.8899493916</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4351247152368227</v>
+        <v>0.474057186760505</v>
       </c>
       <c r="T91">
-        <v>8.991332915400061</v>
+        <v>9.890466206940069</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.003670473764213772</v>
+        <v>0.003629690722389175</v>
       </c>
       <c r="W91">
-        <v>0.2349345022863984</v>
+        <v>0.2349441189276607</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.0142266424969526</v>
+        <v>0.01406856869143092</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2588554257109451</v>
+        <v>0.2607554257109451</v>
       </c>
       <c r="C92">
-        <v>-27.58734231810178</v>
+        <v>-28.250341589226</v>
       </c>
       <c r="D92">
-        <v>18.11365768189822</v>
+        <v>17.98655841077401</v>
       </c>
       <c r="E92">
-        <v>38.341</v>
+        <v>38.87690000000001</v>
       </c>
       <c r="F92">
-        <v>48.231</v>
+        <v>48.76690000000001</v>
       </c>
       <c r="G92">
         <v>2.53</v>
@@ -8956,37 +8956,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M92">
-        <v>11.3728698</v>
+        <v>11.49923502</v>
       </c>
       <c r="N92">
-        <v>-11.2128698</v>
+        <v>-11.33923502</v>
       </c>
       <c r="O92">
-        <v>-2.8929204084</v>
+        <v>-2.925522635160001</v>
       </c>
       <c r="P92">
-        <v>-8.3199493916</v>
+        <v>-8.413712384840002</v>
       </c>
       <c r="Q92">
-        <v>-2.8899493916</v>
+        <v>-2.983712384840002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.474057186760505</v>
+        <v>0.5216413186227834</v>
       </c>
       <c r="T92">
-        <v>9.890466206940069</v>
+        <v>10.98940689660008</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.003629690722389175</v>
+        <v>0.003589804011154129</v>
       </c>
       <c r="W92">
-        <v>0.2349441189276607</v>
+        <v>0.2349535242141698</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.01406856869143092</v>
+        <v>0.01391396903548114</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2607554257109451</v>
+        <v>0.2626554257109451</v>
       </c>
       <c r="C93">
-        <v>-28.250341589226</v>
+        <v>-28.91156963728509</v>
       </c>
       <c r="D93">
-        <v>17.98655841077401</v>
+        <v>17.86123036271492</v>
       </c>
       <c r="E93">
-        <v>38.87690000000001</v>
+        <v>39.4128</v>
       </c>
       <c r="F93">
-        <v>48.76690000000001</v>
+        <v>49.3028</v>
       </c>
       <c r="G93">
         <v>2.53</v>
@@ -9038,37 +9038,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M93">
-        <v>11.49923502</v>
+        <v>11.62560024</v>
       </c>
       <c r="N93">
-        <v>-11.33923502</v>
+        <v>-11.46560024</v>
       </c>
       <c r="O93">
-        <v>-2.925522635160001</v>
+        <v>-2.958124861920001</v>
       </c>
       <c r="P93">
-        <v>-8.413712384840002</v>
+        <v>-8.507475378080002</v>
       </c>
       <c r="Q93">
-        <v>-2.983712384840002</v>
+        <v>-3.077475378080003</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5216413186227834</v>
+        <v>0.5811214834506314</v>
       </c>
       <c r="T93">
-        <v>10.98940689660008</v>
+        <v>12.36308275867509</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.003589804011154129</v>
+        <v>0.003550784402337236</v>
       </c>
       <c r="W93">
-        <v>0.2349535242141698</v>
+        <v>0.2349627250379289</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.01391396903548114</v>
+        <v>0.01376273024161723</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2626554257109451</v>
+        <v>0.2645554257109451</v>
       </c>
       <c r="C94">
-        <v>-28.91156963728509</v>
+        <v>-29.57106323104909</v>
       </c>
       <c r="D94">
-        <v>17.86123036271492</v>
+        <v>17.73763676895091</v>
       </c>
       <c r="E94">
-        <v>39.4128</v>
+        <v>39.9487</v>
       </c>
       <c r="F94">
-        <v>49.3028</v>
+        <v>49.8387</v>
       </c>
       <c r="G94">
         <v>2.53</v>
@@ -9120,37 +9120,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M94">
-        <v>11.62560024</v>
+        <v>11.75196546</v>
       </c>
       <c r="N94">
-        <v>-11.46560024</v>
+        <v>-11.59196546</v>
       </c>
       <c r="O94">
-        <v>-2.958124861920001</v>
+        <v>-2.99072708868</v>
       </c>
       <c r="P94">
-        <v>-8.507475378080002</v>
+        <v>-8.601238371320001</v>
       </c>
       <c r="Q94">
-        <v>-3.077475378080003</v>
+        <v>-3.171238371320001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5811214834506314</v>
+        <v>0.657595981086436</v>
       </c>
       <c r="T94">
-        <v>12.36308275867509</v>
+        <v>14.12923743848582</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.003550784402337236</v>
+        <v>0.00351260392489275</v>
       </c>
       <c r="W94">
-        <v>0.2349627250379289</v>
+        <v>0.2349717279945103</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.01376273024161723</v>
+        <v>0.01361474389493311</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2645554257109451</v>
+        <v>0.2664554257109451</v>
       </c>
       <c r="C95">
-        <v>-29.57106323104909</v>
+        <v>-30.22885812857271</v>
       </c>
       <c r="D95">
-        <v>17.73763676895091</v>
+        <v>17.6157418714273</v>
       </c>
       <c r="E95">
-        <v>39.9487</v>
+        <v>40.48460000000001</v>
       </c>
       <c r="F95">
-        <v>49.8387</v>
+        <v>50.37460000000001</v>
       </c>
       <c r="G95">
         <v>2.53</v>
@@ -9202,37 +9202,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M95">
-        <v>11.75196546</v>
+        <v>11.87833068</v>
       </c>
       <c r="N95">
-        <v>-11.59196546</v>
+        <v>-11.71833068</v>
       </c>
       <c r="O95">
-        <v>-2.99072708868</v>
+        <v>-3.023329315440001</v>
       </c>
       <c r="P95">
-        <v>-8.601238371320001</v>
+        <v>-8.695001364560003</v>
       </c>
       <c r="Q95">
-        <v>-3.171238371320001</v>
+        <v>-3.265001364560003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.657595981086436</v>
+        <v>0.7595619779341755</v>
       </c>
       <c r="T95">
-        <v>14.12923743848582</v>
+        <v>16.48411034490013</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.00351260392489275</v>
+        <v>0.003475235798032189</v>
       </c>
       <c r="W95">
-        <v>0.2349717279945103</v>
+        <v>0.234980539398824</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.01361474389493311</v>
+        <v>0.01346990619392319</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2664554257109451</v>
+        <v>0.2683554257109451</v>
       </c>
       <c r="C96">
-        <v>-30.22885812857271</v>
+        <v>-30.88498911168694</v>
       </c>
       <c r="D96">
-        <v>17.6157418714273</v>
+        <v>17.49551088831307</v>
       </c>
       <c r="E96">
-        <v>40.48460000000001</v>
+        <v>41.02050000000001</v>
       </c>
       <c r="F96">
-        <v>50.37460000000001</v>
+        <v>50.91050000000001</v>
       </c>
       <c r="G96">
         <v>2.53</v>
@@ -9284,37 +9284,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M96">
-        <v>11.87833068</v>
+        <v>12.0046959</v>
       </c>
       <c r="N96">
-        <v>-11.71833068</v>
+        <v>-11.8446959</v>
       </c>
       <c r="O96">
-        <v>-3.023329315440001</v>
+        <v>-3.055931542200001</v>
       </c>
       <c r="P96">
-        <v>-8.695001364560003</v>
+        <v>-8.788764357800002</v>
       </c>
       <c r="Q96">
-        <v>-3.265001364560003</v>
+        <v>-3.358764357800002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7595619779341755</v>
+        <v>0.902314373521011</v>
       </c>
       <c r="T96">
-        <v>16.48411034490013</v>
+        <v>19.78093241388016</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.003475235798032189</v>
+        <v>0.003438654368579219</v>
       </c>
       <c r="W96">
-        <v>0.234980539398824</v>
+        <v>0.234989165299889</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.01346990619392319</v>
+        <v>0.01332811770767139</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2683554257109451</v>
+        <v>0.2702554257109451</v>
       </c>
       <c r="C97">
-        <v>-30.88498911168694</v>
+        <v>-31.53949001908791</v>
       </c>
       <c r="D97">
-        <v>17.49551088831307</v>
+        <v>17.37690998091209</v>
       </c>
       <c r="E97">
-        <v>41.02050000000001</v>
+        <v>41.5564</v>
       </c>
       <c r="F97">
-        <v>50.91050000000001</v>
+        <v>51.4464</v>
       </c>
       <c r="G97">
         <v>2.53</v>
@@ -9366,37 +9366,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M97">
-        <v>12.0046959</v>
+        <v>12.13106112</v>
       </c>
       <c r="N97">
-        <v>-11.8446959</v>
+        <v>-11.97106112</v>
       </c>
       <c r="O97">
-        <v>-3.055931542200001</v>
+        <v>-3.088533768960001</v>
       </c>
       <c r="P97">
-        <v>-8.788764357800002</v>
+        <v>-8.88252735104</v>
       </c>
       <c r="Q97">
-        <v>-3.358764357800002</v>
+        <v>-3.452527351040001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.902314373521011</v>
+        <v>1.116442966901265</v>
       </c>
       <c r="T97">
-        <v>19.78093241388016</v>
+        <v>24.72616551735022</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.003438654368579219</v>
+        <v>0.003402835052239852</v>
       </c>
       <c r="W97">
-        <v>0.234989165299889</v>
+        <v>0.2349976114946819</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.01332811770767139</v>
+        <v>0.01318928314821644</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2702554257109451</v>
+        <v>0.2721554257109451</v>
       </c>
       <c r="C98">
-        <v>-31.53949001908791</v>
+        <v>-32.19239377808884</v>
       </c>
       <c r="D98">
-        <v>17.37690998091209</v>
+        <v>17.25990622191116</v>
       </c>
       <c r="E98">
-        <v>41.5564</v>
+        <v>42.0923</v>
       </c>
       <c r="F98">
-        <v>51.4464</v>
+        <v>51.9823</v>
       </c>
       <c r="G98">
         <v>2.53</v>
@@ -9448,37 +9448,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M98">
-        <v>12.13106112</v>
+        <v>12.25742634</v>
       </c>
       <c r="N98">
-        <v>-11.97106112</v>
+        <v>-12.09742634</v>
       </c>
       <c r="O98">
-        <v>-3.088533768960001</v>
+        <v>-3.12113599572</v>
       </c>
       <c r="P98">
-        <v>-8.88252735104</v>
+        <v>-8.976290344280001</v>
       </c>
       <c r="Q98">
-        <v>-3.452527351040001</v>
+        <v>-3.546290344280001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.116442966901261</v>
+        <v>1.473323955868349</v>
       </c>
       <c r="T98">
-        <v>24.72616551735015</v>
+        <v>32.9682206898002</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.003402835052239852</v>
+        <v>0.00336775427850542</v>
       </c>
       <c r="W98">
-        <v>0.2349976114946819</v>
+        <v>0.2350058835411284</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.01318928314821644</v>
+        <v>0.0130533111569977</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2721554257109451</v>
+        <v>0.2740554257109451</v>
       </c>
       <c r="C99">
-        <v>-32.19239377808884</v>
+        <v>-32.84373243509786</v>
       </c>
       <c r="D99">
-        <v>17.25990622191116</v>
+        <v>17.14446756490214</v>
       </c>
       <c r="E99">
-        <v>42.0923</v>
+        <v>42.6282</v>
       </c>
       <c r="F99">
-        <v>51.9823</v>
+        <v>52.5182</v>
       </c>
       <c r="G99">
         <v>2.53</v>
@@ -9530,37 +9530,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M99">
-        <v>12.25742634</v>
+        <v>12.38379156</v>
       </c>
       <c r="N99">
-        <v>-12.09742634</v>
+        <v>-12.22379156</v>
       </c>
       <c r="O99">
-        <v>-3.12113599572</v>
+        <v>-3.15373822248</v>
       </c>
       <c r="P99">
-        <v>-8.976290344280001</v>
+        <v>-9.070053337520001</v>
       </c>
       <c r="Q99">
-        <v>-3.546290344280001</v>
+        <v>-3.640053337520001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.473323955868349</v>
+        <v>2.187085933802523</v>
       </c>
       <c r="T99">
-        <v>32.9682206898002</v>
+        <v>49.4523310347003</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.00336775427850542</v>
+        <v>0.003333389438928835</v>
       </c>
       <c r="W99">
-        <v>0.2350058835411284</v>
+        <v>0.2350139867703006</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.0130533111569977</v>
+        <v>0.01292011410437532</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2740554257109451</v>
+        <v>0.2759554257109451</v>
       </c>
       <c r="C100">
-        <v>-32.84373243509786</v>
+        <v>-33.49353718488088</v>
       </c>
       <c r="D100">
-        <v>17.14446756490214</v>
+        <v>17.03056281511913</v>
       </c>
       <c r="E100">
-        <v>42.6282</v>
+        <v>43.1641</v>
       </c>
       <c r="F100">
-        <v>52.5182</v>
+        <v>53.05410000000001</v>
       </c>
       <c r="G100">
         <v>2.53</v>
@@ -9612,37 +9612,37 @@
         <v>0.1600000000000001</v>
       </c>
       <c r="M100">
-        <v>12.38379156</v>
+        <v>12.51015678</v>
       </c>
       <c r="N100">
-        <v>-12.22379156</v>
+        <v>-12.35015678</v>
       </c>
       <c r="O100">
-        <v>-3.15373822248</v>
+        <v>-3.186340449240001</v>
       </c>
       <c r="P100">
-        <v>-9.070053337520001</v>
+        <v>-9.163816330760001</v>
       </c>
       <c r="Q100">
-        <v>-3.640053337520001</v>
+        <v>-3.733816330760002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.187085933802523</v>
+        <v>4.328371867605045</v>
       </c>
       <c r="T100">
-        <v>49.4523310347003</v>
+        <v>98.9046620694006</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.003333389438928835</v>
+        <v>0.003299718838535613</v>
       </c>
       <c r="W100">
-        <v>0.2350139867703006</v>
+        <v>0.2350219262978733</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.01292011410437532</v>
+        <v>0.01278960790130079</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2759554257109451</v>
-      </c>
-      <c r="C101">
-        <v>-33.49353718488088</v>
-      </c>
-      <c r="D101">
-        <v>17.03056281511913</v>
-      </c>
-      <c r="E101">
-        <v>43.1641</v>
-      </c>
-      <c r="F101">
-        <v>53.05410000000001</v>
-      </c>
-      <c r="G101">
-        <v>2.53</v>
-      </c>
-      <c r="H101">
-        <v>43.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.59</v>
-      </c>
-      <c r="K101">
-        <v>5.43</v>
-      </c>
-      <c r="L101">
-        <v>0.1600000000000001</v>
-      </c>
-      <c r="M101">
-        <v>12.51015678</v>
-      </c>
-      <c r="N101">
-        <v>-12.35015678</v>
-      </c>
-      <c r="O101">
-        <v>-3.186340449240001</v>
-      </c>
-      <c r="P101">
-        <v>-9.163816330760001</v>
-      </c>
-      <c r="Q101">
-        <v>-3.733816330760002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.328371867605045</v>
-      </c>
-      <c r="T101">
-        <v>98.9046620694006</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.003299718838535613</v>
-      </c>
-      <c r="W101">
-        <v>0.2350219262978733</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.01278960790130079</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
